--- a/SpaceDebris_site_1000/unknown_GRACE_attached_to_Centaur-5_SEC_upper_st.xlsx
+++ b/SpaceDebris_site_1000/unknown_GRACE_attached_to_Centaur-5_SEC_upper_st.xlsx
@@ -452,7002 +452,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104.97</v>
+        <v>0.13</v>
       </c>
       <c r="B2" t="n">
-        <v>45153</v>
+        <v>37580</v>
       </c>
       <c r="C2" t="n">
-        <v>107.51</v>
+        <v>1.38</v>
       </c>
       <c r="D2" t="n">
-        <v>11411</v>
+        <v>24357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102.29</v>
+        <v>0.7</v>
       </c>
       <c r="B3" t="n">
-        <v>49073</v>
+        <v>37894</v>
       </c>
       <c r="C3" t="n">
-        <v>101.27</v>
+        <v>3.22</v>
       </c>
       <c r="D3" t="n">
-        <v>29079</v>
+        <v>25941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92.8</v>
+        <v>1.15</v>
       </c>
       <c r="B4" t="n">
-        <v>31997</v>
+        <v>38045</v>
       </c>
       <c r="C4" t="n">
-        <v>91.23</v>
+        <v>4.36</v>
       </c>
       <c r="D4" t="n">
-        <v>21077</v>
+        <v>13717</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105.74</v>
+        <v>2.34</v>
       </c>
       <c r="B5" t="n">
-        <v>44912</v>
+        <v>36090</v>
       </c>
       <c r="C5" t="n">
-        <v>102.79</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>26749</v>
+        <v>14294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112.45</v>
+        <v>2.39</v>
       </c>
       <c r="B6" t="n">
-        <v>24998</v>
+        <v>37133</v>
       </c>
       <c r="C6" t="n">
-        <v>108.5</v>
+        <v>3.55</v>
       </c>
       <c r="D6" t="n">
-        <v>28878</v>
+        <v>17285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>144.56</v>
+        <v>2.4</v>
       </c>
       <c r="B7" t="n">
-        <v>22355</v>
+        <v>37726</v>
       </c>
       <c r="C7" t="n">
-        <v>143.07</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>12970</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94.42</v>
+        <v>2.43</v>
       </c>
       <c r="B8" t="n">
-        <v>30946</v>
+        <v>37722</v>
       </c>
       <c r="C8" t="n">
-        <v>93.45</v>
+        <v>3.53</v>
       </c>
       <c r="D8" t="n">
-        <v>15052</v>
+        <v>12531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110.84</v>
+        <v>2.52</v>
       </c>
       <c r="B9" t="n">
-        <v>31119</v>
+        <v>35159</v>
       </c>
       <c r="C9" t="n">
-        <v>113.15</v>
+        <v>0.41</v>
       </c>
       <c r="D9" t="n">
-        <v>14940</v>
+        <v>15567</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107.33</v>
+        <v>2.75</v>
       </c>
       <c r="B10" t="n">
-        <v>41607</v>
+        <v>36622</v>
       </c>
       <c r="C10" t="n">
-        <v>110.06</v>
+        <v>6.01</v>
       </c>
       <c r="D10" t="n">
-        <v>25014</v>
+        <v>11023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98.89</v>
+        <v>3.35</v>
       </c>
       <c r="B11" t="n">
-        <v>44240</v>
+        <v>37513</v>
       </c>
       <c r="C11" t="n">
-        <v>100.1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>22368</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119.76</v>
+        <v>3.79</v>
       </c>
       <c r="B12" t="n">
-        <v>25093</v>
+        <v>36552</v>
       </c>
       <c r="C12" t="n">
-        <v>121.82</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>26834</v>
+        <v>24354</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102.2</v>
+        <v>4.01</v>
       </c>
       <c r="B13" t="n">
-        <v>48117</v>
+        <v>34408</v>
       </c>
       <c r="C13" t="n">
-        <v>101.83</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>19250</v>
+        <v>15239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107.92</v>
+        <v>4.05</v>
       </c>
       <c r="B14" t="n">
-        <v>40363</v>
+        <v>35201</v>
       </c>
       <c r="C14" t="n">
-        <v>103.97</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>24148</v>
+        <v>27673</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102.04</v>
+        <v>4.23</v>
       </c>
       <c r="B15" t="n">
-        <v>45581</v>
+        <v>36151</v>
       </c>
       <c r="C15" t="n">
-        <v>105.06</v>
+        <v>3.23</v>
       </c>
       <c r="D15" t="n">
-        <v>18882</v>
+        <v>20115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116.89</v>
+        <v>4.39</v>
       </c>
       <c r="B16" t="n">
-        <v>24800</v>
+        <v>34401</v>
       </c>
       <c r="C16" t="n">
-        <v>115.84</v>
+        <v>9.9</v>
       </c>
       <c r="D16" t="n">
-        <v>10961</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114.06</v>
+        <v>5.48</v>
       </c>
       <c r="B17" t="n">
-        <v>23350</v>
+        <v>34691</v>
       </c>
       <c r="C17" t="n">
-        <v>111.13</v>
+        <v>2.52</v>
       </c>
       <c r="D17" t="n">
-        <v>20392</v>
+        <v>13289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>93.05</v>
+        <v>5.52</v>
       </c>
       <c r="B18" t="n">
-        <v>28792</v>
+        <v>34213</v>
       </c>
       <c r="C18" t="n">
-        <v>91.03</v>
+        <v>3.62</v>
       </c>
       <c r="D18" t="n">
-        <v>22264</v>
+        <v>20246</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95.64</v>
+        <v>5.61</v>
       </c>
       <c r="B19" t="n">
-        <v>35213</v>
+        <v>33472</v>
       </c>
       <c r="C19" t="n">
-        <v>98.90000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="D19" t="n">
-        <v>12801</v>
+        <v>27045</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96.43000000000001</v>
+        <v>5.69</v>
       </c>
       <c r="B20" t="n">
-        <v>36746</v>
+        <v>35100</v>
       </c>
       <c r="C20" t="n">
-        <v>95.41</v>
+        <v>5.32</v>
       </c>
       <c r="D20" t="n">
-        <v>26514</v>
+        <v>23466</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>32.78</v>
+        <v>5.71</v>
       </c>
       <c r="B21" t="n">
-        <v>23108</v>
+        <v>34510</v>
       </c>
       <c r="C21" t="n">
-        <v>32.07</v>
+        <v>1.32</v>
       </c>
       <c r="D21" t="n">
-        <v>12490</v>
+        <v>27359</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101.72</v>
+        <v>6.51</v>
       </c>
       <c r="B22" t="n">
-        <v>48844</v>
+        <v>32514</v>
       </c>
       <c r="C22" t="n">
-        <v>101.12</v>
+        <v>11.31</v>
       </c>
       <c r="D22" t="n">
-        <v>13049</v>
+        <v>29946</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>152.52</v>
+        <v>6.58</v>
       </c>
       <c r="B23" t="n">
-        <v>20405</v>
+        <v>35307</v>
       </c>
       <c r="C23" t="n">
-        <v>152.17</v>
+        <v>14.46</v>
       </c>
       <c r="D23" t="n">
-        <v>27613</v>
+        <v>12242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>100.03</v>
+        <v>6.89</v>
       </c>
       <c r="B24" t="n">
-        <v>43148</v>
+        <v>35260</v>
       </c>
       <c r="C24" t="n">
-        <v>98.56999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="D24" t="n">
-        <v>23406</v>
+        <v>16873</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112.82</v>
+        <v>7.19</v>
       </c>
       <c r="B25" t="n">
-        <v>25240</v>
+        <v>32767</v>
       </c>
       <c r="C25" t="n">
-        <v>109.44</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>16566</v>
+        <v>16764</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103.19</v>
+        <v>7.7</v>
       </c>
       <c r="B26" t="n">
-        <v>44793</v>
+        <v>34516</v>
       </c>
       <c r="C26" t="n">
-        <v>105.61</v>
+        <v>9.52</v>
       </c>
       <c r="D26" t="n">
-        <v>21586</v>
+        <v>13035</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>108.77</v>
+        <v>7.82</v>
       </c>
       <c r="B27" t="n">
-        <v>37028</v>
+        <v>33759</v>
       </c>
       <c r="C27" t="n">
-        <v>111.87</v>
+        <v>4.99</v>
       </c>
       <c r="D27" t="n">
-        <v>14646</v>
+        <v>20940</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>93.84</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="B28" t="n">
-        <v>32431</v>
+        <v>31275</v>
       </c>
       <c r="C28" t="n">
-        <v>95.93000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="D28" t="n">
-        <v>27027</v>
+        <v>14087</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110.86</v>
+        <v>8.82</v>
       </c>
       <c r="B29" t="n">
-        <v>28347</v>
+        <v>33779</v>
       </c>
       <c r="C29" t="n">
-        <v>106.58</v>
+        <v>10.9</v>
       </c>
       <c r="D29" t="n">
-        <v>12826</v>
+        <v>27093</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104.86</v>
+        <v>9.85</v>
       </c>
       <c r="B30" t="n">
-        <v>48639</v>
+        <v>32109</v>
       </c>
       <c r="C30" t="n">
-        <v>101.17</v>
+        <v>10.8</v>
       </c>
       <c r="D30" t="n">
-        <v>24541</v>
+        <v>17196</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>92.26000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="B31" t="n">
-        <v>24607</v>
+        <v>27164</v>
       </c>
       <c r="C31" t="n">
-        <v>90.37</v>
+        <v>4.77</v>
       </c>
       <c r="D31" t="n">
-        <v>26535</v>
+        <v>18787</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97.02</v>
+        <v>11.59</v>
       </c>
       <c r="B32" t="n">
-        <v>39182</v>
+        <v>28976</v>
       </c>
       <c r="C32" t="n">
-        <v>94.27</v>
+        <v>22.82</v>
       </c>
       <c r="D32" t="n">
-        <v>13568</v>
+        <v>14560</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>97.41</v>
+        <v>11.91</v>
       </c>
       <c r="B33" t="n">
-        <v>39449</v>
+        <v>30401</v>
       </c>
       <c r="C33" t="n">
-        <v>94.56</v>
+        <v>10.95</v>
       </c>
       <c r="D33" t="n">
-        <v>27341</v>
+        <v>10822</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>93.61</v>
+        <v>12.45</v>
       </c>
       <c r="B34" t="n">
-        <v>29788</v>
+        <v>28086</v>
       </c>
       <c r="C34" t="n">
-        <v>96.12</v>
+        <v>15.33</v>
       </c>
       <c r="D34" t="n">
-        <v>25894</v>
+        <v>25805</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91.48999999999999</v>
+        <v>13.56</v>
       </c>
       <c r="B35" t="n">
-        <v>24679</v>
+        <v>29444</v>
       </c>
       <c r="C35" t="n">
-        <v>94.8</v>
+        <v>13.61</v>
       </c>
       <c r="D35" t="n">
-        <v>19089</v>
+        <v>23584</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99.41</v>
+        <v>15.07</v>
       </c>
       <c r="B36" t="n">
-        <v>41199</v>
+        <v>27212</v>
       </c>
       <c r="C36" t="n">
-        <v>99.94</v>
+        <v>14.94</v>
       </c>
       <c r="D36" t="n">
-        <v>28666</v>
+        <v>28637</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>93.16</v>
+        <v>15.13</v>
       </c>
       <c r="B37" t="n">
-        <v>30816</v>
+        <v>24259</v>
       </c>
       <c r="C37" t="n">
-        <v>92.95999999999999</v>
+        <v>28.74</v>
       </c>
       <c r="D37" t="n">
-        <v>21829</v>
+        <v>11229</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105.19</v>
+        <v>15.48</v>
       </c>
       <c r="B38" t="n">
-        <v>46508</v>
+        <v>29758</v>
       </c>
       <c r="C38" t="n">
-        <v>108.69</v>
+        <v>18.13</v>
       </c>
       <c r="D38" t="n">
-        <v>23048</v>
+        <v>19819</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>114.27</v>
+        <v>15.77</v>
       </c>
       <c r="B39" t="n">
-        <v>23280</v>
+        <v>28421</v>
       </c>
       <c r="C39" t="n">
-        <v>118.11</v>
+        <v>4.41</v>
       </c>
       <c r="D39" t="n">
-        <v>29786</v>
+        <v>16093</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>107.73</v>
+        <v>15.83</v>
       </c>
       <c r="B40" t="n">
-        <v>39457</v>
+        <v>26878</v>
       </c>
       <c r="C40" t="n">
-        <v>108.58</v>
+        <v>15</v>
       </c>
       <c r="D40" t="n">
-        <v>15383</v>
+        <v>24682</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>140.74</v>
+        <v>15.92</v>
       </c>
       <c r="B41" t="n">
-        <v>23606</v>
+        <v>23922</v>
       </c>
       <c r="C41" t="n">
-        <v>135.94</v>
+        <v>16.09</v>
       </c>
       <c r="D41" t="n">
-        <v>28381</v>
+        <v>23874</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>146.11</v>
+        <v>15.99</v>
       </c>
       <c r="B42" t="n">
-        <v>22233</v>
+        <v>25392</v>
       </c>
       <c r="C42" t="n">
-        <v>140.53</v>
+        <v>16.05</v>
       </c>
       <c r="D42" t="n">
-        <v>15411</v>
+        <v>18023</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110.39</v>
+        <v>17.2</v>
       </c>
       <c r="B43" t="n">
-        <v>30195</v>
+        <v>26527</v>
       </c>
       <c r="C43" t="n">
-        <v>108.36</v>
+        <v>26.06</v>
       </c>
       <c r="D43" t="n">
-        <v>10677</v>
+        <v>15325</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>92.59999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="B44" t="n">
-        <v>25980</v>
+        <v>24369</v>
       </c>
       <c r="C44" t="n">
-        <v>95.18000000000001</v>
+        <v>18.7</v>
       </c>
       <c r="D44" t="n">
-        <v>19255</v>
+        <v>16034</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110.55</v>
+        <v>17.51</v>
       </c>
       <c r="B45" t="n">
-        <v>29301</v>
+        <v>25315</v>
       </c>
       <c r="C45" t="n">
-        <v>110.36</v>
+        <v>20.32</v>
       </c>
       <c r="D45" t="n">
-        <v>13640</v>
+        <v>20755</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>114.91</v>
+        <v>17.56</v>
       </c>
       <c r="B46" t="n">
-        <v>24098</v>
+        <v>24267</v>
       </c>
       <c r="C46" t="n">
-        <v>114.55</v>
+        <v>10.63</v>
       </c>
       <c r="D46" t="n">
-        <v>19782</v>
+        <v>21341</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111.79</v>
+        <v>18.28</v>
       </c>
       <c r="B47" t="n">
-        <v>28895</v>
+        <v>23970</v>
       </c>
       <c r="C47" t="n">
-        <v>114.89</v>
+        <v>10.25</v>
       </c>
       <c r="D47" t="n">
-        <v>13457</v>
+        <v>25101</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105.12</v>
+        <v>18.32</v>
       </c>
       <c r="B48" t="n">
-        <v>45716</v>
+        <v>23734</v>
       </c>
       <c r="C48" t="n">
-        <v>103.54</v>
+        <v>11.14</v>
       </c>
       <c r="D48" t="n">
-        <v>25808</v>
+        <v>20116</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>108.61</v>
+        <v>18.68</v>
       </c>
       <c r="B49" t="n">
-        <v>37446</v>
+        <v>22930</v>
       </c>
       <c r="C49" t="n">
-        <v>112.69</v>
+        <v>21.05</v>
       </c>
       <c r="D49" t="n">
-        <v>28139</v>
+        <v>26300</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104.58</v>
+        <v>18.83</v>
       </c>
       <c r="B50" t="n">
-        <v>46730</v>
+        <v>23649</v>
       </c>
       <c r="C50" t="n">
-        <v>103.5</v>
+        <v>24.42</v>
       </c>
       <c r="D50" t="n">
-        <v>16726</v>
+        <v>29475</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>108.5</v>
+        <v>19.37</v>
       </c>
       <c r="B51" t="n">
-        <v>33457</v>
+        <v>22583</v>
       </c>
       <c r="C51" t="n">
-        <v>112.21</v>
+        <v>23.13</v>
       </c>
       <c r="D51" t="n">
-        <v>17373</v>
+        <v>11815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>93.93000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="B52" t="n">
-        <v>30081</v>
+        <v>23880</v>
       </c>
       <c r="C52" t="n">
-        <v>96.67</v>
+        <v>21.1</v>
       </c>
       <c r="D52" t="n">
-        <v>24497</v>
+        <v>14628</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>93.13</v>
+        <v>19.4</v>
       </c>
       <c r="B53" t="n">
-        <v>30005</v>
+        <v>23997</v>
       </c>
       <c r="C53" t="n">
-        <v>96.17</v>
+        <v>19.91</v>
       </c>
       <c r="D53" t="n">
-        <v>26887</v>
+        <v>24379</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>99.92</v>
+        <v>20.1</v>
       </c>
       <c r="B54" t="n">
-        <v>44203</v>
+        <v>22920</v>
       </c>
       <c r="C54" t="n">
-        <v>97.86</v>
+        <v>22.47</v>
       </c>
       <c r="D54" t="n">
-        <v>19964</v>
+        <v>18804</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>72.87</v>
+        <v>20.26</v>
       </c>
       <c r="B55" t="n">
-        <v>22129</v>
+        <v>25662</v>
       </c>
       <c r="C55" t="n">
-        <v>70.66</v>
+        <v>12.65</v>
       </c>
       <c r="D55" t="n">
-        <v>21912</v>
+        <v>21617</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101.77</v>
+        <v>20.34</v>
       </c>
       <c r="B56" t="n">
-        <v>44782</v>
+        <v>23302</v>
       </c>
       <c r="C56" t="n">
-        <v>99.63</v>
+        <v>21.75</v>
       </c>
       <c r="D56" t="n">
-        <v>28981</v>
+        <v>11960</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>105.34</v>
+        <v>21.63</v>
       </c>
       <c r="B57" t="n">
-        <v>46241</v>
+        <v>23007</v>
       </c>
       <c r="C57" t="n">
-        <v>103.11</v>
+        <v>27.64</v>
       </c>
       <c r="D57" t="n">
-        <v>27697</v>
+        <v>19161</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>96.34999999999999</v>
+        <v>21.65</v>
       </c>
       <c r="B58" t="n">
-        <v>37219</v>
+        <v>22292</v>
       </c>
       <c r="C58" t="n">
-        <v>93.51000000000001</v>
+        <v>24.98</v>
       </c>
       <c r="D58" t="n">
-        <v>18487</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>100.21</v>
+        <v>21.8</v>
       </c>
       <c r="B59" t="n">
-        <v>43252</v>
+        <v>23760</v>
       </c>
       <c r="C59" t="n">
-        <v>98.02</v>
+        <v>21.49</v>
       </c>
       <c r="D59" t="n">
-        <v>24304</v>
+        <v>24727</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>99.52</v>
+        <v>22.02</v>
       </c>
       <c r="B60" t="n">
-        <v>43213</v>
+        <v>21486</v>
       </c>
       <c r="C60" t="n">
-        <v>101.72</v>
+        <v>25.56</v>
       </c>
       <c r="D60" t="n">
-        <v>12025</v>
+        <v>16793</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>110.65</v>
+        <v>22.16</v>
       </c>
       <c r="B61" t="n">
-        <v>28403</v>
+        <v>20763</v>
       </c>
       <c r="C61" t="n">
-        <v>113.14</v>
+        <v>27.09</v>
       </c>
       <c r="D61" t="n">
-        <v>18192</v>
+        <v>24831</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>100.23</v>
+        <v>22.19</v>
       </c>
       <c r="B62" t="n">
-        <v>46025</v>
+        <v>23341</v>
       </c>
       <c r="C62" t="n">
-        <v>98.77</v>
+        <v>21.53</v>
       </c>
       <c r="D62" t="n">
-        <v>14526</v>
+        <v>12220</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>106.9</v>
+        <v>22.59</v>
       </c>
       <c r="B63" t="n">
-        <v>41667</v>
+        <v>23224</v>
       </c>
       <c r="C63" t="n">
-        <v>108.78</v>
+        <v>28.7</v>
       </c>
       <c r="D63" t="n">
-        <v>10698</v>
+        <v>12625</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>91.27</v>
+        <v>22.81</v>
       </c>
       <c r="B64" t="n">
-        <v>25177</v>
+        <v>23161</v>
       </c>
       <c r="C64" t="n">
-        <v>90.73999999999999</v>
+        <v>19.17</v>
       </c>
       <c r="D64" t="n">
-        <v>19432</v>
+        <v>18615</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>95.66</v>
+        <v>23.52</v>
       </c>
       <c r="B65" t="n">
-        <v>38523</v>
+        <v>21087</v>
       </c>
       <c r="C65" t="n">
-        <v>97.51000000000001</v>
+        <v>34.95</v>
       </c>
       <c r="D65" t="n">
-        <v>12639</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>111.17</v>
+        <v>24.37</v>
       </c>
       <c r="B66" t="n">
-        <v>28161</v>
+        <v>21303</v>
       </c>
       <c r="C66" t="n">
-        <v>109.62</v>
+        <v>21.2</v>
       </c>
       <c r="D66" t="n">
-        <v>24471</v>
+        <v>13563</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>114.76</v>
+        <v>24.6</v>
       </c>
       <c r="B67" t="n">
-        <v>26506</v>
+        <v>22128</v>
       </c>
       <c r="C67" t="n">
-        <v>115.36</v>
+        <v>21.05</v>
       </c>
       <c r="D67" t="n">
-        <v>13912</v>
+        <v>18461</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109.46</v>
+        <v>24.92</v>
       </c>
       <c r="B68" t="n">
-        <v>33356</v>
+        <v>21476</v>
       </c>
       <c r="C68" t="n">
-        <v>109.95</v>
+        <v>32.06</v>
       </c>
       <c r="D68" t="n">
-        <v>16592</v>
+        <v>14929</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96.48999999999999</v>
+        <v>25.31</v>
       </c>
       <c r="B69" t="n">
-        <v>35371</v>
+        <v>23082</v>
       </c>
       <c r="C69" t="n">
-        <v>97.70999999999999</v>
+        <v>26.01</v>
       </c>
       <c r="D69" t="n">
-        <v>22444</v>
+        <v>14507</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>97.26000000000001</v>
+        <v>25.54</v>
       </c>
       <c r="B70" t="n">
-        <v>38920</v>
+        <v>24174</v>
       </c>
       <c r="C70" t="n">
-        <v>98.02</v>
+        <v>28.44</v>
       </c>
       <c r="D70" t="n">
-        <v>28960</v>
+        <v>27385</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>98.52</v>
+        <v>26.13</v>
       </c>
       <c r="B71" t="n">
-        <v>42069</v>
+        <v>22058</v>
       </c>
       <c r="C71" t="n">
-        <v>101.32</v>
+        <v>20.7</v>
       </c>
       <c r="D71" t="n">
-        <v>23067</v>
+        <v>27903</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>114.44</v>
+        <v>26.27</v>
       </c>
       <c r="B72" t="n">
-        <v>24659</v>
+        <v>23601</v>
       </c>
       <c r="C72" t="n">
-        <v>112.98</v>
+        <v>44.89</v>
       </c>
       <c r="D72" t="n">
-        <v>15452</v>
+        <v>11730</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>108.34</v>
+        <v>26.72</v>
       </c>
       <c r="B73" t="n">
-        <v>34467</v>
+        <v>21110</v>
       </c>
       <c r="C73" t="n">
-        <v>111.19</v>
+        <v>25.47</v>
       </c>
       <c r="D73" t="n">
-        <v>10868</v>
+        <v>28239</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5.72</v>
+        <v>27.39</v>
       </c>
       <c r="B74" t="n">
-        <v>23634</v>
+        <v>27339</v>
       </c>
       <c r="C74" t="n">
-        <v>6.33</v>
+        <v>23.02</v>
       </c>
       <c r="D74" t="n">
-        <v>12825</v>
+        <v>24817</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>107.92</v>
+        <v>27.42</v>
       </c>
       <c r="B75" t="n">
-        <v>39505</v>
+        <v>21400</v>
       </c>
       <c r="C75" t="n">
-        <v>110.5</v>
+        <v>17.6</v>
       </c>
       <c r="D75" t="n">
-        <v>15294</v>
+        <v>25533</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98.26000000000001</v>
+        <v>27.82</v>
       </c>
       <c r="B76" t="n">
-        <v>42823</v>
+        <v>19759</v>
       </c>
       <c r="C76" t="n">
-        <v>95.53</v>
+        <v>22.96</v>
       </c>
       <c r="D76" t="n">
-        <v>25207</v>
+        <v>20600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>102.35</v>
+        <v>28.17</v>
       </c>
       <c r="B77" t="n">
-        <v>46436</v>
+        <v>23818</v>
       </c>
       <c r="C77" t="n">
-        <v>103.67</v>
+        <v>31.62</v>
       </c>
       <c r="D77" t="n">
-        <v>16222</v>
+        <v>11968</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>109.25</v>
+        <v>28.34</v>
       </c>
       <c r="B78" t="n">
-        <v>32258</v>
+        <v>23148</v>
       </c>
       <c r="C78" t="n">
-        <v>111.86</v>
+        <v>34.82</v>
       </c>
       <c r="D78" t="n">
-        <v>27744</v>
+        <v>16094</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>102.34</v>
+        <v>28.59</v>
       </c>
       <c r="B79" t="n">
-        <v>47170</v>
+        <v>21970</v>
       </c>
       <c r="C79" t="n">
-        <v>105.97</v>
+        <v>30.31</v>
       </c>
       <c r="D79" t="n">
-        <v>22925</v>
+        <v>14376</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>97.78</v>
+        <v>28.96</v>
       </c>
       <c r="B80" t="n">
-        <v>41046</v>
+        <v>20551</v>
       </c>
       <c r="C80" t="n">
-        <v>100.6</v>
+        <v>20.59</v>
       </c>
       <c r="D80" t="n">
-        <v>21593</v>
+        <v>23123</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>96.83</v>
+        <v>29.21</v>
       </c>
       <c r="B81" t="n">
-        <v>38705</v>
+        <v>18073</v>
       </c>
       <c r="C81" t="n">
-        <v>99.86</v>
+        <v>29.09</v>
       </c>
       <c r="D81" t="n">
-        <v>17077</v>
+        <v>14210</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>114.46</v>
+        <v>30.4</v>
       </c>
       <c r="B82" t="n">
-        <v>23234</v>
+        <v>17065</v>
       </c>
       <c r="C82" t="n">
-        <v>112.19</v>
+        <v>40.41</v>
       </c>
       <c r="D82" t="n">
-        <v>20987</v>
+        <v>14442</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>103.83</v>
+        <v>30.67</v>
       </c>
       <c r="B83" t="n">
-        <v>45432</v>
+        <v>22819</v>
       </c>
       <c r="C83" t="n">
-        <v>107.48</v>
+        <v>40.13</v>
       </c>
       <c r="D83" t="n">
-        <v>21740</v>
+        <v>29448</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>101.44</v>
+        <v>30.68</v>
       </c>
       <c r="B84" t="n">
-        <v>46007</v>
+        <v>18371</v>
       </c>
       <c r="C84" t="n">
-        <v>97.84999999999999</v>
+        <v>28.75</v>
       </c>
       <c r="D84" t="n">
-        <v>14681</v>
+        <v>25101</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>107.81</v>
+        <v>30.93</v>
       </c>
       <c r="B85" t="n">
-        <v>38712</v>
+        <v>22820</v>
       </c>
       <c r="C85" t="n">
-        <v>104.22</v>
+        <v>30.31</v>
       </c>
       <c r="D85" t="n">
-        <v>25239</v>
+        <v>23095</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>168.03</v>
+        <v>30.93</v>
       </c>
       <c r="B86" t="n">
-        <v>22312</v>
+        <v>22124</v>
       </c>
       <c r="C86" t="n">
-        <v>169.46</v>
+        <v>28.4</v>
       </c>
       <c r="D86" t="n">
-        <v>22533</v>
+        <v>21288</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>106.69</v>
+        <v>31.14</v>
       </c>
       <c r="B87" t="n">
-        <v>44186</v>
+        <v>22539</v>
       </c>
       <c r="C87" t="n">
-        <v>105.43</v>
+        <v>31.87</v>
       </c>
       <c r="D87" t="n">
-        <v>11958</v>
+        <v>22775</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>67.13</v>
+        <v>31.84</v>
       </c>
       <c r="B88" t="n">
-        <v>23344</v>
+        <v>20713</v>
       </c>
       <c r="C88" t="n">
-        <v>66.2</v>
+        <v>41.86</v>
       </c>
       <c r="D88" t="n">
-        <v>17621</v>
+        <v>13876</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>97.54000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="B89" t="n">
-        <v>43650</v>
+        <v>21840</v>
       </c>
       <c r="C89" t="n">
-        <v>98.76000000000001</v>
+        <v>30.03</v>
       </c>
       <c r="D89" t="n">
-        <v>25195</v>
+        <v>28878</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>102.75</v>
+        <v>32.63</v>
       </c>
       <c r="B90" t="n">
-        <v>45827</v>
+        <v>23527</v>
       </c>
       <c r="C90" t="n">
-        <v>103</v>
+        <v>21.73</v>
       </c>
       <c r="D90" t="n">
-        <v>20711</v>
+        <v>25723</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>100.22</v>
+        <v>32.69</v>
       </c>
       <c r="B91" t="n">
-        <v>46225</v>
+        <v>20411</v>
       </c>
       <c r="C91" t="n">
-        <v>100.99</v>
+        <v>19.73</v>
       </c>
       <c r="D91" t="n">
-        <v>26534</v>
+        <v>19466</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>100.7</v>
+        <v>32.7</v>
       </c>
       <c r="B92" t="n">
-        <v>47734</v>
+        <v>24195</v>
       </c>
       <c r="C92" t="n">
-        <v>103.8</v>
+        <v>21.29</v>
       </c>
       <c r="D92" t="n">
-        <v>25444</v>
+        <v>26908</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>95.7</v>
+        <v>32.73</v>
       </c>
       <c r="B93" t="n">
-        <v>35587</v>
+        <v>18493</v>
       </c>
       <c r="C93" t="n">
-        <v>98.72</v>
+        <v>41.89</v>
       </c>
       <c r="D93" t="n">
-        <v>19495</v>
+        <v>21656</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>101.01</v>
+        <v>33.15</v>
       </c>
       <c r="B94" t="n">
-        <v>45747</v>
+        <v>24286</v>
       </c>
       <c r="C94" t="n">
-        <v>100.22</v>
+        <v>34.27</v>
       </c>
       <c r="D94" t="n">
-        <v>14996</v>
+        <v>15731</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>90.04000000000001</v>
+        <v>33.22</v>
       </c>
       <c r="B95" t="n">
-        <v>22030</v>
+        <v>20279</v>
       </c>
       <c r="C95" t="n">
-        <v>92.3</v>
+        <v>36.4</v>
       </c>
       <c r="D95" t="n">
-        <v>11152</v>
+        <v>27786</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>103.51</v>
+        <v>34.23</v>
       </c>
       <c r="B96" t="n">
-        <v>48330</v>
+        <v>20985</v>
       </c>
       <c r="C96" t="n">
-        <v>105.24</v>
+        <v>42.69</v>
       </c>
       <c r="D96" t="n">
-        <v>22485</v>
+        <v>22625</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>107.33</v>
+        <v>34.25</v>
       </c>
       <c r="B97" t="n">
-        <v>39040</v>
+        <v>22001</v>
       </c>
       <c r="C97" t="n">
-        <v>104.22</v>
+        <v>33.21</v>
       </c>
       <c r="D97" t="n">
-        <v>11946</v>
+        <v>12954</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>110.29</v>
+        <v>34.32</v>
       </c>
       <c r="B98" t="n">
-        <v>32551</v>
+        <v>21665</v>
       </c>
       <c r="C98" t="n">
-        <v>113.39</v>
+        <v>40.41</v>
       </c>
       <c r="D98" t="n">
-        <v>29869</v>
+        <v>29032</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>100.79</v>
+        <v>34.42</v>
       </c>
       <c r="B99" t="n">
-        <v>49055</v>
+        <v>19915</v>
       </c>
       <c r="C99" t="n">
-        <v>102.14</v>
+        <v>37.94</v>
       </c>
       <c r="D99" t="n">
-        <v>15416</v>
+        <v>24226</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>90.41</v>
+        <v>34.55</v>
       </c>
       <c r="B100" t="n">
-        <v>24758</v>
+        <v>22720</v>
       </c>
       <c r="C100" t="n">
-        <v>93.56</v>
+        <v>42.86</v>
       </c>
       <c r="D100" t="n">
-        <v>19106</v>
+        <v>19252</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>111.28</v>
+        <v>34.77</v>
       </c>
       <c r="B101" t="n">
-        <v>26890</v>
+        <v>20233</v>
       </c>
       <c r="C101" t="n">
-        <v>111.96</v>
+        <v>22.13</v>
       </c>
       <c r="D101" t="n">
-        <v>29592</v>
+        <v>19054</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110.71</v>
+        <v>34.81</v>
       </c>
       <c r="B102" t="n">
-        <v>30423</v>
+        <v>20745</v>
       </c>
       <c r="C102" t="n">
-        <v>112.57</v>
+        <v>33.2</v>
       </c>
       <c r="D102" t="n">
-        <v>25256</v>
+        <v>22393</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>98.53</v>
+        <v>34.87</v>
       </c>
       <c r="B103" t="n">
-        <v>41697</v>
+        <v>20257</v>
       </c>
       <c r="C103" t="n">
-        <v>96.09999999999999</v>
+        <v>24.79</v>
       </c>
       <c r="D103" t="n">
-        <v>25164</v>
+        <v>10124</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>166.45</v>
+        <v>35.02</v>
       </c>
       <c r="B104" t="n">
-        <v>21376</v>
+        <v>22203</v>
       </c>
       <c r="C104" t="n">
-        <v>171.97</v>
+        <v>34.13</v>
       </c>
       <c r="D104" t="n">
-        <v>13465</v>
+        <v>27838</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>103.26</v>
+        <v>35.05</v>
       </c>
       <c r="B105" t="n">
-        <v>46893</v>
+        <v>21231</v>
       </c>
       <c r="C105" t="n">
-        <v>105.04</v>
+        <v>31.66</v>
       </c>
       <c r="D105" t="n">
-        <v>22525</v>
+        <v>22641</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>97.68000000000001</v>
+        <v>35.94</v>
       </c>
       <c r="B106" t="n">
-        <v>41675</v>
+        <v>22309</v>
       </c>
       <c r="C106" t="n">
-        <v>101.41</v>
+        <v>38.41</v>
       </c>
       <c r="D106" t="n">
-        <v>13723</v>
+        <v>12806</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>94.29000000000001</v>
+        <v>36.38</v>
       </c>
       <c r="B107" t="n">
-        <v>32520</v>
+        <v>24576</v>
       </c>
       <c r="C107" t="n">
-        <v>97.59999999999999</v>
+        <v>37.25</v>
       </c>
       <c r="D107" t="n">
-        <v>26086</v>
+        <v>14591</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112.84</v>
+        <v>36.38</v>
       </c>
       <c r="B108" t="n">
-        <v>27688</v>
+        <v>22342</v>
       </c>
       <c r="C108" t="n">
-        <v>115.81</v>
+        <v>41.11</v>
       </c>
       <c r="D108" t="n">
-        <v>17371</v>
+        <v>22928</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>94.92</v>
+        <v>36.51</v>
       </c>
       <c r="B109" t="n">
-        <v>30975</v>
+        <v>18286</v>
       </c>
       <c r="C109" t="n">
-        <v>91.81</v>
+        <v>41.01</v>
       </c>
       <c r="D109" t="n">
-        <v>14128</v>
+        <v>25866</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>96.89</v>
+        <v>37.55</v>
       </c>
       <c r="B110" t="n">
-        <v>39546</v>
+        <v>18866</v>
       </c>
       <c r="C110" t="n">
-        <v>94.81999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="D110" t="n">
-        <v>26668</v>
+        <v>18132</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>103.95</v>
+        <v>37.97</v>
       </c>
       <c r="B111" t="n">
-        <v>46911</v>
+        <v>20128</v>
       </c>
       <c r="C111" t="n">
-        <v>105.42</v>
+        <v>34.42</v>
       </c>
       <c r="D111" t="n">
-        <v>21839</v>
+        <v>15024</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>103.38</v>
+        <v>37.97</v>
       </c>
       <c r="B112" t="n">
-        <v>44912</v>
+        <v>17986</v>
       </c>
       <c r="C112" t="n">
-        <v>105.14</v>
+        <v>33.28</v>
       </c>
       <c r="D112" t="n">
-        <v>17126</v>
+        <v>13624</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>154.85</v>
+        <v>38.63</v>
       </c>
       <c r="B113" t="n">
-        <v>23588</v>
+        <v>22303</v>
       </c>
       <c r="C113" t="n">
-        <v>159.09</v>
+        <v>31.81</v>
       </c>
       <c r="D113" t="n">
-        <v>17851</v>
+        <v>19788</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>102.57</v>
+        <v>38.78</v>
       </c>
       <c r="B114" t="n">
-        <v>48911</v>
+        <v>20939</v>
       </c>
       <c r="C114" t="n">
-        <v>104.25</v>
+        <v>43.2</v>
       </c>
       <c r="D114" t="n">
-        <v>12611</v>
+        <v>14716</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>35.91</v>
+        <v>39.32</v>
       </c>
       <c r="B115" t="n">
-        <v>24372</v>
+        <v>20151</v>
       </c>
       <c r="C115" t="n">
-        <v>34.9</v>
+        <v>34.47</v>
       </c>
       <c r="D115" t="n">
-        <v>15569</v>
+        <v>12381</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>160.47</v>
+        <v>39.46</v>
       </c>
       <c r="B116" t="n">
-        <v>24644</v>
+        <v>24986</v>
       </c>
       <c r="C116" t="n">
-        <v>156.37</v>
+        <v>44.96</v>
       </c>
       <c r="D116" t="n">
-        <v>20067</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>108.12</v>
+        <v>39.67</v>
       </c>
       <c r="B117" t="n">
-        <v>35903</v>
+        <v>19334</v>
       </c>
       <c r="C117" t="n">
-        <v>106.95</v>
+        <v>48.74</v>
       </c>
       <c r="D117" t="n">
-        <v>25426</v>
+        <v>29970</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>104.43</v>
+        <v>40.4</v>
       </c>
       <c r="B118" t="n">
-        <v>46557</v>
+        <v>22168</v>
       </c>
       <c r="C118" t="n">
-        <v>103.77</v>
+        <v>32.16</v>
       </c>
       <c r="D118" t="n">
-        <v>29215</v>
+        <v>18922</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>112.74</v>
+        <v>41</v>
       </c>
       <c r="B119" t="n">
-        <v>25341</v>
+        <v>21544</v>
       </c>
       <c r="C119" t="n">
-        <v>112.38</v>
+        <v>31.18</v>
       </c>
       <c r="D119" t="n">
-        <v>14283</v>
+        <v>25645</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>103.22</v>
+        <v>41.5</v>
       </c>
       <c r="B120" t="n">
-        <v>48027</v>
+        <v>21093</v>
       </c>
       <c r="C120" t="n">
-        <v>101.28</v>
+        <v>36.47</v>
       </c>
       <c r="D120" t="n">
-        <v>12017</v>
+        <v>13555</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>94.84999999999999</v>
+        <v>41.69</v>
       </c>
       <c r="B121" t="n">
-        <v>31384</v>
+        <v>20322</v>
       </c>
       <c r="C121" t="n">
-        <v>93.28</v>
+        <v>40.87</v>
       </c>
       <c r="D121" t="n">
-        <v>27837</v>
+        <v>14304</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>90.38</v>
+        <v>41.71</v>
       </c>
       <c r="B122" t="n">
-        <v>22256</v>
+        <v>22375</v>
       </c>
       <c r="C122" t="n">
-        <v>89.05</v>
+        <v>37.64</v>
       </c>
       <c r="D122" t="n">
-        <v>14299</v>
+        <v>22925</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103.31</v>
+        <v>42.13</v>
       </c>
       <c r="B123" t="n">
-        <v>46366</v>
+        <v>16671</v>
       </c>
       <c r="C123" t="n">
-        <v>99.34999999999999</v>
+        <v>42.21</v>
       </c>
       <c r="D123" t="n">
-        <v>22062</v>
+        <v>22760</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>111.15</v>
+        <v>42.39</v>
       </c>
       <c r="B124" t="n">
-        <v>29516</v>
+        <v>22615</v>
       </c>
       <c r="C124" t="n">
-        <v>109.55</v>
+        <v>45.91</v>
       </c>
       <c r="D124" t="n">
-        <v>15006</v>
+        <v>15817</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>97.45</v>
+        <v>42.44</v>
       </c>
       <c r="B125" t="n">
-        <v>39381</v>
+        <v>20186</v>
       </c>
       <c r="C125" t="n">
-        <v>93.27</v>
+        <v>48.79</v>
       </c>
       <c r="D125" t="n">
-        <v>21944</v>
+        <v>19529</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>106.07</v>
+        <v>42.8</v>
       </c>
       <c r="B126" t="n">
-        <v>42681</v>
+        <v>23106</v>
       </c>
       <c r="C126" t="n">
-        <v>105.14</v>
+        <v>33.12</v>
       </c>
       <c r="D126" t="n">
-        <v>10294</v>
+        <v>11168</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>97.31999999999999</v>
+        <v>42.86</v>
       </c>
       <c r="B127" t="n">
-        <v>36834</v>
+        <v>22089</v>
       </c>
       <c r="C127" t="n">
-        <v>95.31</v>
+        <v>36.14</v>
       </c>
       <c r="D127" t="n">
-        <v>11367</v>
+        <v>16620</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>113.7</v>
+        <v>43.04</v>
       </c>
       <c r="B128" t="n">
-        <v>23774</v>
+        <v>20484</v>
       </c>
       <c r="C128" t="n">
-        <v>110.06</v>
+        <v>34.21</v>
       </c>
       <c r="D128" t="n">
-        <v>10253</v>
+        <v>28838</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>112.64</v>
+        <v>43.23</v>
       </c>
       <c r="B129" t="n">
-        <v>27884</v>
+        <v>22104</v>
       </c>
       <c r="C129" t="n">
-        <v>108.42</v>
+        <v>34.39</v>
       </c>
       <c r="D129" t="n">
-        <v>16399</v>
+        <v>20057</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>19.11</v>
+        <v>43.39</v>
       </c>
       <c r="B130" t="n">
-        <v>23101</v>
+        <v>21835</v>
       </c>
       <c r="C130" t="n">
-        <v>20.66</v>
+        <v>41.55</v>
       </c>
       <c r="D130" t="n">
-        <v>16668</v>
+        <v>21533</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>108.65</v>
+        <v>43.67</v>
       </c>
       <c r="B131" t="n">
-        <v>34674</v>
+        <v>20125</v>
       </c>
       <c r="C131" t="n">
-        <v>111.79</v>
+        <v>38.24</v>
       </c>
       <c r="D131" t="n">
-        <v>11851</v>
+        <v>16294</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>105.49</v>
+        <v>43.77</v>
       </c>
       <c r="B132" t="n">
-        <v>46486</v>
+        <v>23261</v>
       </c>
       <c r="C132" t="n">
-        <v>108.12</v>
+        <v>42.59</v>
       </c>
       <c r="D132" t="n">
-        <v>15594</v>
+        <v>16703</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>91.63</v>
+        <v>44.09</v>
       </c>
       <c r="B133" t="n">
-        <v>22789</v>
+        <v>21091</v>
       </c>
       <c r="C133" t="n">
-        <v>90.17</v>
+        <v>50</v>
       </c>
       <c r="D133" t="n">
-        <v>27249</v>
+        <v>21763</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>112.45</v>
+        <v>44.93</v>
       </c>
       <c r="B134" t="n">
-        <v>27418</v>
+        <v>19245</v>
       </c>
       <c r="C134" t="n">
-        <v>115.52</v>
+        <v>50.02</v>
       </c>
       <c r="D134" t="n">
-        <v>17169</v>
+        <v>24215</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>97.28</v>
+        <v>46.03</v>
       </c>
       <c r="B135" t="n">
-        <v>38613</v>
+        <v>21795</v>
       </c>
       <c r="C135" t="n">
-        <v>97.31</v>
+        <v>47.12</v>
       </c>
       <c r="D135" t="n">
-        <v>24495</v>
+        <v>29307</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>157.79</v>
+        <v>46.35</v>
       </c>
       <c r="B136" t="n">
-        <v>20074</v>
+        <v>21888</v>
       </c>
       <c r="C136" t="n">
-        <v>160.4</v>
+        <v>50.29</v>
       </c>
       <c r="D136" t="n">
-        <v>25354</v>
+        <v>28066</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>105.42</v>
+        <v>46.37</v>
       </c>
       <c r="B137" t="n">
-        <v>45425</v>
+        <v>20763</v>
       </c>
       <c r="C137" t="n">
-        <v>102.63</v>
+        <v>40.68</v>
       </c>
       <c r="D137" t="n">
-        <v>13648</v>
+        <v>15647</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>113.06</v>
+        <v>46.5</v>
       </c>
       <c r="B138" t="n">
-        <v>24660</v>
+        <v>18748</v>
       </c>
       <c r="C138" t="n">
-        <v>115.51</v>
+        <v>50.18</v>
       </c>
       <c r="D138" t="n">
-        <v>25983</v>
+        <v>15909</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>103.1</v>
+        <v>46.92</v>
       </c>
       <c r="B139" t="n">
-        <v>44988</v>
+        <v>20845</v>
       </c>
       <c r="C139" t="n">
-        <v>100.77</v>
+        <v>46.54</v>
       </c>
       <c r="D139" t="n">
-        <v>29338</v>
+        <v>23917</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>20.19</v>
+        <v>47.14</v>
       </c>
       <c r="B140" t="n">
-        <v>24886</v>
+        <v>22708</v>
       </c>
       <c r="C140" t="n">
-        <v>20.79</v>
+        <v>44.64</v>
       </c>
       <c r="D140" t="n">
-        <v>27768</v>
+        <v>23349</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>95.95</v>
+        <v>47.22</v>
       </c>
       <c r="B141" t="n">
-        <v>36286</v>
+        <v>20596</v>
       </c>
       <c r="C141" t="n">
-        <v>97.06999999999999</v>
+        <v>54.25</v>
       </c>
       <c r="D141" t="n">
-        <v>24168</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>112.94</v>
+        <v>47.57</v>
       </c>
       <c r="B142" t="n">
-        <v>25562</v>
+        <v>20994</v>
       </c>
       <c r="C142" t="n">
-        <v>110.59</v>
+        <v>42.09</v>
       </c>
       <c r="D142" t="n">
-        <v>26412</v>
+        <v>11256</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>103.98</v>
+        <v>48.36</v>
       </c>
       <c r="B143" t="n">
-        <v>48354</v>
+        <v>22633</v>
       </c>
       <c r="C143" t="n">
-        <v>103.52</v>
+        <v>34.9</v>
       </c>
       <c r="D143" t="n">
-        <v>28968</v>
+        <v>26425</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>110.96</v>
+        <v>48.98</v>
       </c>
       <c r="B144" t="n">
-        <v>29383</v>
+        <v>23246</v>
       </c>
       <c r="C144" t="n">
-        <v>111.5</v>
+        <v>45.12</v>
       </c>
       <c r="D144" t="n">
-        <v>27100</v>
+        <v>18197</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>68.65000000000001</v>
+        <v>49.44</v>
       </c>
       <c r="B145" t="n">
-        <v>21239</v>
+        <v>20698</v>
       </c>
       <c r="C145" t="n">
-        <v>67.17</v>
+        <v>50.66</v>
       </c>
       <c r="D145" t="n">
-        <v>17947</v>
+        <v>10901</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>105.21</v>
+        <v>49.5</v>
       </c>
       <c r="B146" t="n">
-        <v>45019</v>
+        <v>21352</v>
       </c>
       <c r="C146" t="n">
-        <v>106.7</v>
+        <v>55.04</v>
       </c>
       <c r="D146" t="n">
-        <v>10559</v>
+        <v>16237</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>106.68</v>
+        <v>49.76</v>
       </c>
       <c r="B147" t="n">
-        <v>40114</v>
+        <v>19278</v>
       </c>
       <c r="C147" t="n">
-        <v>103.93</v>
+        <v>59.03</v>
       </c>
       <c r="D147" t="n">
-        <v>16437</v>
+        <v>23085</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>172.98</v>
+        <v>49.77</v>
       </c>
       <c r="B148" t="n">
-        <v>22141</v>
+        <v>22949</v>
       </c>
       <c r="C148" t="n">
-        <v>168.26</v>
+        <v>45.09</v>
       </c>
       <c r="D148" t="n">
-        <v>10833</v>
+        <v>16611</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>53.92</v>
+        <v>50.09</v>
       </c>
       <c r="B149" t="n">
-        <v>20994</v>
+        <v>19591</v>
       </c>
       <c r="C149" t="n">
-        <v>54.5</v>
+        <v>58.12</v>
       </c>
       <c r="D149" t="n">
-        <v>17190</v>
+        <v>26502</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>101.54</v>
+        <v>50.43</v>
       </c>
       <c r="B150" t="n">
-        <v>46426</v>
+        <v>19987</v>
       </c>
       <c r="C150" t="n">
-        <v>104.37</v>
+        <v>45.1</v>
       </c>
       <c r="D150" t="n">
-        <v>16381</v>
+        <v>22040</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>162.84</v>
+        <v>50.61</v>
       </c>
       <c r="B151" t="n">
-        <v>22144</v>
+        <v>20722</v>
       </c>
       <c r="C151" t="n">
-        <v>164.64</v>
+        <v>53.57</v>
       </c>
       <c r="D151" t="n">
-        <v>11857</v>
+        <v>18261</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121.36</v>
+        <v>51.09</v>
       </c>
       <c r="B152" t="n">
-        <v>23890</v>
+        <v>21386</v>
       </c>
       <c r="C152" t="n">
-        <v>119.72</v>
+        <v>43.22</v>
       </c>
       <c r="D152" t="n">
-        <v>23960</v>
+        <v>10228</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>92.11</v>
+        <v>51.3</v>
       </c>
       <c r="B153" t="n">
-        <v>27019</v>
+        <v>21439</v>
       </c>
       <c r="C153" t="n">
-        <v>93.31</v>
+        <v>61.49</v>
       </c>
       <c r="D153" t="n">
-        <v>28552</v>
+        <v>15497</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>102.23</v>
+        <v>51.34</v>
       </c>
       <c r="B154" t="n">
-        <v>46583</v>
+        <v>20828</v>
       </c>
       <c r="C154" t="n">
-        <v>105.33</v>
+        <v>42.55</v>
       </c>
       <c r="D154" t="n">
-        <v>24350</v>
+        <v>23003</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>101.11</v>
+        <v>51.82</v>
       </c>
       <c r="B155" t="n">
-        <v>45078</v>
+        <v>20158</v>
       </c>
       <c r="C155" t="n">
-        <v>102.08</v>
+        <v>49.51</v>
       </c>
       <c r="D155" t="n">
-        <v>25589</v>
+        <v>15752</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>156.5</v>
+        <v>52.36</v>
       </c>
       <c r="B156" t="n">
-        <v>24314</v>
+        <v>22384</v>
       </c>
       <c r="C156" t="n">
-        <v>153.1</v>
+        <v>50.94</v>
       </c>
       <c r="D156" t="n">
-        <v>11918</v>
+        <v>24183</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>110.77</v>
+        <v>52.61</v>
       </c>
       <c r="B157" t="n">
-        <v>30197</v>
+        <v>20485</v>
       </c>
       <c r="C157" t="n">
-        <v>105.93</v>
+        <v>47.18</v>
       </c>
       <c r="D157" t="n">
-        <v>21434</v>
+        <v>14729</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>114.82</v>
+        <v>53.02</v>
       </c>
       <c r="B158" t="n">
-        <v>22131</v>
+        <v>21507</v>
       </c>
       <c r="C158" t="n">
-        <v>117.94</v>
+        <v>52.5</v>
       </c>
       <c r="D158" t="n">
-        <v>13047</v>
+        <v>10312</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>100.83</v>
+        <v>53.03</v>
       </c>
       <c r="B159" t="n">
-        <v>44521</v>
+        <v>22288</v>
       </c>
       <c r="C159" t="n">
-        <v>100</v>
+        <v>53.06</v>
       </c>
       <c r="D159" t="n">
-        <v>25290</v>
+        <v>27420</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>92.16</v>
+        <v>53.42</v>
       </c>
       <c r="B160" t="n">
-        <v>27483</v>
+        <v>21443</v>
       </c>
       <c r="C160" t="n">
-        <v>94.75</v>
+        <v>62.99</v>
       </c>
       <c r="D160" t="n">
-        <v>21627</v>
+        <v>13460</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>77.73999999999999</v>
+        <v>54.49</v>
       </c>
       <c r="B161" t="n">
-        <v>22389</v>
+        <v>21998</v>
       </c>
       <c r="C161" t="n">
-        <v>74.97</v>
+        <v>62.95</v>
       </c>
       <c r="D161" t="n">
-        <v>21606</v>
+        <v>22979</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>51.7</v>
+        <v>54.56</v>
       </c>
       <c r="B162" t="n">
-        <v>24722</v>
+        <v>21866</v>
       </c>
       <c r="C162" t="n">
-        <v>49.78</v>
+        <v>55.9</v>
       </c>
       <c r="D162" t="n">
-        <v>21337</v>
+        <v>13447</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>94.55</v>
+        <v>54.67</v>
       </c>
       <c r="B163" t="n">
-        <v>31260</v>
+        <v>21953</v>
       </c>
       <c r="C163" t="n">
-        <v>92.3</v>
+        <v>70.47</v>
       </c>
       <c r="D163" t="n">
-        <v>19177</v>
+        <v>20065</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>92.15000000000001</v>
+        <v>55.68</v>
       </c>
       <c r="B164" t="n">
-        <v>27421</v>
+        <v>21872</v>
       </c>
       <c r="C164" t="n">
-        <v>89.18000000000001</v>
+        <v>62.02</v>
       </c>
       <c r="D164" t="n">
-        <v>22793</v>
+        <v>24313</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>111.45</v>
+        <v>56.41</v>
       </c>
       <c r="B165" t="n">
-        <v>29688</v>
+        <v>23325</v>
       </c>
       <c r="C165" t="n">
-        <v>111.86</v>
+        <v>50.74</v>
       </c>
       <c r="D165" t="n">
-        <v>11444</v>
+        <v>17662</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>109.86</v>
+        <v>56.69</v>
       </c>
       <c r="B166" t="n">
-        <v>35978</v>
+        <v>20949</v>
       </c>
       <c r="C166" t="n">
-        <v>105.98</v>
+        <v>61.95</v>
       </c>
       <c r="D166" t="n">
-        <v>10314</v>
+        <v>29393</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>114.22</v>
+        <v>56.75</v>
       </c>
       <c r="B167" t="n">
-        <v>24199</v>
+        <v>21767</v>
       </c>
       <c r="C167" t="n">
-        <v>111.78</v>
+        <v>71.13</v>
       </c>
       <c r="D167" t="n">
-        <v>16321</v>
+        <v>23955</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>104.8</v>
+        <v>57.14</v>
       </c>
       <c r="B168" t="n">
-        <v>47121</v>
+        <v>20799</v>
       </c>
       <c r="C168" t="n">
-        <v>105.25</v>
+        <v>60.47</v>
       </c>
       <c r="D168" t="n">
-        <v>26968</v>
+        <v>17961</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>102.03</v>
+        <v>57.69</v>
       </c>
       <c r="B169" t="n">
-        <v>47319</v>
+        <v>22190</v>
       </c>
       <c r="C169" t="n">
-        <v>98.95</v>
+        <v>68.87</v>
       </c>
       <c r="D169" t="n">
-        <v>13525</v>
+        <v>20113</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>162</v>
+        <v>57.98</v>
       </c>
       <c r="B170" t="n">
-        <v>24014</v>
+        <v>20947</v>
       </c>
       <c r="C170" t="n">
-        <v>165.1</v>
+        <v>59.15</v>
       </c>
       <c r="D170" t="n">
-        <v>10660</v>
+        <v>11873</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>16.14</v>
+        <v>58.24</v>
       </c>
       <c r="B171" t="n">
-        <v>23788</v>
+        <v>21424</v>
       </c>
       <c r="C171" t="n">
-        <v>16.15</v>
+        <v>65.03</v>
       </c>
       <c r="D171" t="n">
-        <v>29042</v>
+        <v>21795</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>106.1</v>
+        <v>58.32</v>
       </c>
       <c r="B172" t="n">
-        <v>43838</v>
+        <v>19516</v>
       </c>
       <c r="C172" t="n">
-        <v>106.04</v>
+        <v>58.79</v>
       </c>
       <c r="D172" t="n">
-        <v>11448</v>
+        <v>15074</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>100.9</v>
+        <v>58.66</v>
       </c>
       <c r="B173" t="n">
-        <v>44878</v>
+        <v>20333</v>
       </c>
       <c r="C173" t="n">
-        <v>101.93</v>
+        <v>53.54</v>
       </c>
       <c r="D173" t="n">
-        <v>14023</v>
+        <v>16746</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>97.54000000000001</v>
+        <v>59.97</v>
       </c>
       <c r="B174" t="n">
-        <v>39859</v>
+        <v>20607</v>
       </c>
       <c r="C174" t="n">
-        <v>101.48</v>
+        <v>57.1</v>
       </c>
       <c r="D174" t="n">
-        <v>29259</v>
+        <v>22158</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118.82</v>
+        <v>60.06</v>
       </c>
       <c r="B175" t="n">
-        <v>19149</v>
+        <v>20435</v>
       </c>
       <c r="C175" t="n">
-        <v>123.17</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="D175" t="n">
-        <v>22513</v>
+        <v>19550</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>95.17</v>
+        <v>60.44</v>
       </c>
       <c r="B176" t="n">
-        <v>35797</v>
+        <v>19229</v>
       </c>
       <c r="C176" t="n">
-        <v>94.84999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="D176" t="n">
-        <v>25633</v>
+        <v>23072</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>6.71</v>
+        <v>60.76</v>
       </c>
       <c r="B177" t="n">
-        <v>26808</v>
+        <v>20255</v>
       </c>
       <c r="C177" t="n">
-        <v>6.38</v>
+        <v>65.91</v>
       </c>
       <c r="D177" t="n">
-        <v>20626</v>
+        <v>14147</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>90.84999999999999</v>
+        <v>61.09</v>
       </c>
       <c r="B178" t="n">
-        <v>24955</v>
+        <v>21283</v>
       </c>
       <c r="C178" t="n">
-        <v>87.01000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="D178" t="n">
-        <v>16261</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>79.95</v>
+        <v>61.12</v>
       </c>
       <c r="B179" t="n">
-        <v>23604</v>
+        <v>19883</v>
       </c>
       <c r="C179" t="n">
-        <v>82.06</v>
+        <v>65.02</v>
       </c>
       <c r="D179" t="n">
-        <v>24447</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>97.34</v>
+        <v>61.13</v>
       </c>
       <c r="B180" t="n">
-        <v>38767</v>
+        <v>20671</v>
       </c>
       <c r="C180" t="n">
-        <v>94.47</v>
+        <v>45.47</v>
       </c>
       <c r="D180" t="n">
-        <v>29175</v>
+        <v>11324</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>98.33</v>
+        <v>63.1</v>
       </c>
       <c r="B181" t="n">
-        <v>42015</v>
+        <v>19590</v>
       </c>
       <c r="C181" t="n">
-        <v>94.62</v>
+        <v>60.19</v>
       </c>
       <c r="D181" t="n">
-        <v>12395</v>
+        <v>29517</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>98.48999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="B182" t="n">
-        <v>40073</v>
+        <v>22183</v>
       </c>
       <c r="C182" t="n">
-        <v>100.61</v>
+        <v>64.92</v>
       </c>
       <c r="D182" t="n">
-        <v>15682</v>
+        <v>13726</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>102.43</v>
+        <v>63.96</v>
       </c>
       <c r="B183" t="n">
-        <v>48064</v>
+        <v>20152</v>
       </c>
       <c r="C183" t="n">
-        <v>103.65</v>
+        <v>71.8</v>
       </c>
       <c r="D183" t="n">
-        <v>10923</v>
+        <v>10813</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>110.11</v>
+        <v>63.96</v>
       </c>
       <c r="B184" t="n">
-        <v>32569</v>
+        <v>20341</v>
       </c>
       <c r="C184" t="n">
-        <v>113.5</v>
+        <v>57.13</v>
       </c>
       <c r="D184" t="n">
-        <v>20143</v>
+        <v>12921</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>101.57</v>
+        <v>64.44</v>
       </c>
       <c r="B185" t="n">
-        <v>47253</v>
+        <v>21119</v>
       </c>
       <c r="C185" t="n">
-        <v>102.26</v>
+        <v>66.47</v>
       </c>
       <c r="D185" t="n">
-        <v>25380</v>
+        <v>27965</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>73.04000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="B186" t="n">
-        <v>25994</v>
+        <v>20233</v>
       </c>
       <c r="C186" t="n">
-        <v>73.89</v>
+        <v>49.85</v>
       </c>
       <c r="D186" t="n">
-        <v>28559</v>
+        <v>25752</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>111.41</v>
+        <v>64.86</v>
       </c>
       <c r="B187" t="n">
-        <v>30459</v>
+        <v>20142</v>
       </c>
       <c r="C187" t="n">
-        <v>112.55</v>
+        <v>82.5</v>
       </c>
       <c r="D187" t="n">
-        <v>18740</v>
+        <v>27783</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>103.34</v>
+        <v>64.88</v>
       </c>
       <c r="B188" t="n">
-        <v>46065</v>
+        <v>20332</v>
       </c>
       <c r="C188" t="n">
-        <v>104.26</v>
+        <v>59.66</v>
       </c>
       <c r="D188" t="n">
-        <v>12911</v>
+        <v>11464</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>97.86</v>
+        <v>65.09</v>
       </c>
       <c r="B189" t="n">
-        <v>42307</v>
+        <v>21283</v>
       </c>
       <c r="C189" t="n">
-        <v>99.14</v>
+        <v>66.36</v>
       </c>
       <c r="D189" t="n">
-        <v>21129</v>
+        <v>20675</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>112.69</v>
+        <v>65.12</v>
       </c>
       <c r="B190" t="n">
-        <v>26318</v>
+        <v>19717</v>
       </c>
       <c r="C190" t="n">
-        <v>111.63</v>
+        <v>54.3</v>
       </c>
       <c r="D190" t="n">
-        <v>11222</v>
+        <v>13791</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>108.6</v>
+        <v>65.95</v>
       </c>
       <c r="B191" t="n">
-        <v>36705</v>
+        <v>20805</v>
       </c>
       <c r="C191" t="n">
-        <v>106.44</v>
+        <v>59.95</v>
       </c>
       <c r="D191" t="n">
-        <v>12239</v>
+        <v>21987</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>97.55</v>
+        <v>66.23</v>
       </c>
       <c r="B192" t="n">
-        <v>39291</v>
+        <v>20192</v>
       </c>
       <c r="C192" t="n">
-        <v>100.44</v>
+        <v>53.2</v>
       </c>
       <c r="D192" t="n">
-        <v>14721</v>
+        <v>22522</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>111.47</v>
+        <v>66.86</v>
       </c>
       <c r="B193" t="n">
-        <v>28383</v>
+        <v>21433</v>
       </c>
       <c r="C193" t="n">
-        <v>114.87</v>
+        <v>55.41</v>
       </c>
       <c r="D193" t="n">
-        <v>29847</v>
+        <v>25335</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>111.56</v>
+        <v>67.02</v>
       </c>
       <c r="B194" t="n">
-        <v>28424</v>
+        <v>19995</v>
       </c>
       <c r="C194" t="n">
-        <v>115.4</v>
+        <v>70.25</v>
       </c>
       <c r="D194" t="n">
-        <v>27778</v>
+        <v>18878</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>110.13</v>
+        <v>67.19</v>
       </c>
       <c r="B195" t="n">
-        <v>31998</v>
+        <v>21204</v>
       </c>
       <c r="C195" t="n">
-        <v>110.39</v>
+        <v>59.67</v>
       </c>
       <c r="D195" t="n">
-        <v>29508</v>
+        <v>26119</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>96.2</v>
+        <v>67.48</v>
       </c>
       <c r="B196" t="n">
-        <v>36755</v>
+        <v>20108</v>
       </c>
       <c r="C196" t="n">
-        <v>99.5</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D196" t="n">
-        <v>14383</v>
+        <v>12249</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>93.04000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="B197" t="n">
-        <v>32296</v>
+        <v>18680</v>
       </c>
       <c r="C197" t="n">
-        <v>93.17</v>
+        <v>63.34</v>
       </c>
       <c r="D197" t="n">
-        <v>15562</v>
+        <v>10160</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129.92</v>
+        <v>69.33</v>
       </c>
       <c r="B198" t="n">
-        <v>23024</v>
+        <v>20685</v>
       </c>
       <c r="C198" t="n">
-        <v>130.8</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="D198" t="n">
-        <v>21271</v>
+        <v>19895</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>56.72</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="B199" t="n">
-        <v>22925</v>
+        <v>21875</v>
       </c>
       <c r="C199" t="n">
-        <v>59.21</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D199" t="n">
-        <v>28325</v>
+        <v>17139</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>91.84999999999999</v>
+        <v>69.59</v>
       </c>
       <c r="B200" t="n">
-        <v>24989</v>
+        <v>21063</v>
       </c>
       <c r="C200" t="n">
-        <v>94.73</v>
+        <v>59.82</v>
       </c>
       <c r="D200" t="n">
-        <v>28626</v>
+        <v>20384</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>71.26000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="B201" t="n">
-        <v>25973</v>
+        <v>20523</v>
       </c>
       <c r="C201" t="n">
-        <v>69.94</v>
+        <v>51.3</v>
       </c>
       <c r="D201" t="n">
-        <v>21349</v>
+        <v>11227</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>100.09</v>
+        <v>70.33</v>
       </c>
       <c r="B202" t="n">
-        <v>42557</v>
+        <v>20228</v>
       </c>
       <c r="C202" t="n">
-        <v>101.91</v>
+        <v>71.41</v>
       </c>
       <c r="D202" t="n">
-        <v>25641</v>
+        <v>16216</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>103.2</v>
+        <v>70.55</v>
       </c>
       <c r="B203" t="n">
-        <v>46691</v>
+        <v>20594</v>
       </c>
       <c r="C203" t="n">
-        <v>102.38</v>
+        <v>56.63</v>
       </c>
       <c r="D203" t="n">
-        <v>17192</v>
+        <v>12430</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>105.21</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="B204" t="n">
-        <v>45235</v>
+        <v>20038</v>
       </c>
       <c r="C204" t="n">
-        <v>107.41</v>
+        <v>54.79</v>
       </c>
       <c r="D204" t="n">
-        <v>29174</v>
+        <v>17568</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>106.99</v>
+        <v>71.25</v>
       </c>
       <c r="B205" t="n">
-        <v>40435</v>
+        <v>20274</v>
       </c>
       <c r="C205" t="n">
-        <v>103.08</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>24041</v>
+        <v>26409</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>101.39</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="B206" t="n">
-        <v>44181</v>
+        <v>19575</v>
       </c>
       <c r="C206" t="n">
-        <v>97.94</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="D206" t="n">
-        <v>20281</v>
+        <v>21675</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>94.83</v>
+        <v>72.28</v>
       </c>
       <c r="B207" t="n">
-        <v>32052</v>
+        <v>20715</v>
       </c>
       <c r="C207" t="n">
-        <v>97.43000000000001</v>
+        <v>68.16</v>
       </c>
       <c r="D207" t="n">
-        <v>12478</v>
+        <v>16082</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>91.59999999999999</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="B208" t="n">
-        <v>23413</v>
+        <v>21447</v>
       </c>
       <c r="C208" t="n">
-        <v>88.06</v>
+        <v>72.36</v>
       </c>
       <c r="D208" t="n">
-        <v>23434</v>
+        <v>21947</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>113.18</v>
+        <v>73.02</v>
       </c>
       <c r="B209" t="n">
-        <v>22410</v>
+        <v>20354</v>
       </c>
       <c r="C209" t="n">
-        <v>113.07</v>
+        <v>77.39</v>
       </c>
       <c r="D209" t="n">
-        <v>29115</v>
+        <v>23806</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>109.22</v>
+        <v>73.62</v>
       </c>
       <c r="B210" t="n">
-        <v>34563</v>
+        <v>19472</v>
       </c>
       <c r="C210" t="n">
-        <v>112.51</v>
+        <v>81.28</v>
       </c>
       <c r="D210" t="n">
-        <v>17848</v>
+        <v>28672</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>102.49</v>
+        <v>74.42</v>
       </c>
       <c r="B211" t="n">
-        <v>47239</v>
+        <v>21333</v>
       </c>
       <c r="C211" t="n">
-        <v>105.97</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="D211" t="n">
-        <v>21632</v>
+        <v>14524</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>105.01</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="B212" t="n">
-        <v>45378</v>
+        <v>20909</v>
       </c>
       <c r="C212" t="n">
-        <v>104.85</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="D212" t="n">
-        <v>24351</v>
+        <v>17232</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>107.81</v>
+        <v>74.98</v>
       </c>
       <c r="B213" t="n">
-        <v>35453</v>
+        <v>20842</v>
       </c>
       <c r="C213" t="n">
-        <v>108.06</v>
+        <v>71.03</v>
       </c>
       <c r="D213" t="n">
-        <v>29995</v>
+        <v>10870</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>99.47</v>
+        <v>75.39</v>
       </c>
       <c r="B214" t="n">
-        <v>44987</v>
+        <v>20889</v>
       </c>
       <c r="C214" t="n">
-        <v>100.24</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="D214" t="n">
-        <v>24234</v>
+        <v>17893</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>99.86</v>
+        <v>75.97</v>
       </c>
       <c r="B215" t="n">
-        <v>46006</v>
+        <v>20456</v>
       </c>
       <c r="C215" t="n">
-        <v>98.12</v>
+        <v>55.31</v>
       </c>
       <c r="D215" t="n">
-        <v>26790</v>
+        <v>22711</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>110.15</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="B216" t="n">
-        <v>31787</v>
+        <v>20310</v>
       </c>
       <c r="C216" t="n">
-        <v>111.27</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="D216" t="n">
-        <v>21889</v>
+        <v>24108</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>98.88</v>
+        <v>76.72</v>
       </c>
       <c r="B217" t="n">
-        <v>44313</v>
+        <v>20857</v>
       </c>
       <c r="C217" t="n">
-        <v>97.15000000000001</v>
+        <v>73.66</v>
       </c>
       <c r="D217" t="n">
-        <v>16073</v>
+        <v>21982</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>99.5</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="B218" t="n">
-        <v>44180</v>
+        <v>20621</v>
       </c>
       <c r="C218" t="n">
-        <v>101.38</v>
+        <v>92.75</v>
       </c>
       <c r="D218" t="n">
-        <v>12872</v>
+        <v>20654</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>107.12</v>
+        <v>76.92</v>
       </c>
       <c r="B219" t="n">
-        <v>41600</v>
+        <v>21011</v>
       </c>
       <c r="C219" t="n">
-        <v>107.66</v>
+        <v>71.09</v>
       </c>
       <c r="D219" t="n">
-        <v>13958</v>
+        <v>23076</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>26.91</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="B220" t="n">
-        <v>22085</v>
+        <v>20075</v>
       </c>
       <c r="C220" t="n">
-        <v>27.76</v>
+        <v>88.89</v>
       </c>
       <c r="D220" t="n">
-        <v>11196</v>
+        <v>20268</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>95.37</v>
+        <v>77.16</v>
       </c>
       <c r="B221" t="n">
-        <v>35856</v>
+        <v>22121</v>
       </c>
       <c r="C221" t="n">
-        <v>95.67</v>
+        <v>68.33</v>
       </c>
       <c r="D221" t="n">
-        <v>20052</v>
+        <v>17344</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>102.01</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="B222" t="n">
-        <v>46321</v>
+        <v>19245</v>
       </c>
       <c r="C222" t="n">
-        <v>103.98</v>
+        <v>82.53</v>
       </c>
       <c r="D222" t="n">
-        <v>13281</v>
+        <v>17792</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>103.91</v>
+        <v>78.19</v>
       </c>
       <c r="B223" t="n">
-        <v>50642</v>
+        <v>20829</v>
       </c>
       <c r="C223" t="n">
-        <v>104.23</v>
+        <v>86.69</v>
       </c>
       <c r="D223" t="n">
-        <v>17976</v>
+        <v>16033</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>176.42</v>
+        <v>78.39</v>
       </c>
       <c r="B224" t="n">
-        <v>25855</v>
+        <v>20885</v>
       </c>
       <c r="C224" t="n">
-        <v>178.12</v>
+        <v>82.25</v>
       </c>
       <c r="D224" t="n">
-        <v>15147</v>
+        <v>18173</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>91.95</v>
+        <v>78.44</v>
       </c>
       <c r="B225" t="n">
-        <v>27169</v>
+        <v>20405</v>
       </c>
       <c r="C225" t="n">
-        <v>88.95</v>
+        <v>81.44</v>
       </c>
       <c r="D225" t="n">
-        <v>10690</v>
+        <v>20177</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>96.23</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="B226" t="n">
-        <v>37037</v>
+        <v>20846</v>
       </c>
       <c r="C226" t="n">
-        <v>99.81999999999999</v>
+        <v>79.52</v>
       </c>
       <c r="D226" t="n">
-        <v>16472</v>
+        <v>27533</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>90.34</v>
+        <v>78.8</v>
       </c>
       <c r="B227" t="n">
-        <v>23760</v>
+        <v>19559</v>
       </c>
       <c r="C227" t="n">
-        <v>86.05</v>
+        <v>70.59</v>
       </c>
       <c r="D227" t="n">
-        <v>16817</v>
+        <v>12979</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>113.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="B228" t="n">
-        <v>24864</v>
+        <v>20115</v>
       </c>
       <c r="C228" t="n">
-        <v>112.88</v>
+        <v>62.73</v>
       </c>
       <c r="D228" t="n">
-        <v>16791</v>
+        <v>20823</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>113.02</v>
+        <v>79.05</v>
       </c>
       <c r="B229" t="n">
-        <v>24443</v>
+        <v>19883</v>
       </c>
       <c r="C229" t="n">
-        <v>112.18</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="D229" t="n">
-        <v>28618</v>
+        <v>24373</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>91.40000000000001</v>
+        <v>79.72</v>
       </c>
       <c r="B230" t="n">
-        <v>26340</v>
+        <v>19919</v>
       </c>
       <c r="C230" t="n">
-        <v>92.58</v>
+        <v>69.95</v>
       </c>
       <c r="D230" t="n">
-        <v>15768</v>
+        <v>29603</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>14.97</v>
+        <v>79.88</v>
       </c>
       <c r="B231" t="n">
-        <v>23501</v>
+        <v>20158</v>
       </c>
       <c r="C231" t="n">
-        <v>15.43</v>
+        <v>61.54</v>
       </c>
       <c r="D231" t="n">
-        <v>19487</v>
+        <v>29993</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>102.14</v>
+        <v>80.56</v>
       </c>
       <c r="B232" t="n">
-        <v>47188</v>
+        <v>19820</v>
       </c>
       <c r="C232" t="n">
-        <v>103.85</v>
+        <v>96.33</v>
       </c>
       <c r="D232" t="n">
-        <v>29248</v>
+        <v>19769</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>103.34</v>
+        <v>81.17</v>
       </c>
       <c r="B233" t="n">
-        <v>46692</v>
+        <v>20484</v>
       </c>
       <c r="C233" t="n">
-        <v>104.5</v>
+        <v>79.87</v>
       </c>
       <c r="D233" t="n">
-        <v>15687</v>
+        <v>24290</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>107.89</v>
+        <v>81.78</v>
       </c>
       <c r="B234" t="n">
-        <v>39694</v>
+        <v>21352</v>
       </c>
       <c r="C234" t="n">
-        <v>109.49</v>
+        <v>74.31</v>
       </c>
       <c r="D234" t="n">
-        <v>23453</v>
+        <v>17359</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>95.68000000000001</v>
+        <v>81.91</v>
       </c>
       <c r="B235" t="n">
-        <v>34575</v>
+        <v>21077</v>
       </c>
       <c r="C235" t="n">
-        <v>93.01000000000001</v>
+        <v>87.89</v>
       </c>
       <c r="D235" t="n">
-        <v>26809</v>
+        <v>28817</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>109.21</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="B236" t="n">
-        <v>35114</v>
+        <v>20032</v>
       </c>
       <c r="C236" t="n">
-        <v>107.31</v>
+        <v>70.06</v>
       </c>
       <c r="D236" t="n">
-        <v>22088</v>
+        <v>28918</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>93.75</v>
+        <v>82.98</v>
       </c>
       <c r="B237" t="n">
-        <v>28267</v>
+        <v>20707</v>
       </c>
       <c r="C237" t="n">
-        <v>90.59999999999999</v>
+        <v>94.02</v>
       </c>
       <c r="D237" t="n">
-        <v>28463</v>
+        <v>25793</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>92.54000000000001</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="B238" t="n">
-        <v>26122</v>
+        <v>20889</v>
       </c>
       <c r="C238" t="n">
-        <v>90.53</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="D238" t="n">
-        <v>16319</v>
+        <v>21365</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>74.98</v>
+        <v>83.25</v>
       </c>
       <c r="B239" t="n">
-        <v>23281</v>
+        <v>19614</v>
       </c>
       <c r="C239" t="n">
-        <v>76.67</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="D239" t="n">
-        <v>14052</v>
+        <v>16846</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>102.35</v>
+        <v>83.47</v>
       </c>
       <c r="B240" t="n">
-        <v>48028</v>
+        <v>20158</v>
       </c>
       <c r="C240" t="n">
-        <v>103.69</v>
+        <v>88.94</v>
       </c>
       <c r="D240" t="n">
-        <v>26431</v>
+        <v>15845</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>91.79000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="B241" t="n">
-        <v>25800</v>
+        <v>20107</v>
       </c>
       <c r="C241" t="n">
-        <v>89.25</v>
+        <v>94.36</v>
       </c>
       <c r="D241" t="n">
-        <v>28788</v>
+        <v>11196</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>97.38</v>
+        <v>84.44</v>
       </c>
       <c r="B242" t="n">
-        <v>37608</v>
+        <v>20208</v>
       </c>
       <c r="C242" t="n">
-        <v>100.5</v>
+        <v>65.92</v>
       </c>
       <c r="D242" t="n">
-        <v>25916</v>
+        <v>20089</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>95.7</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="B243" t="n">
-        <v>36607</v>
+        <v>20096</v>
       </c>
       <c r="C243" t="n">
-        <v>92.94</v>
+        <v>91.62</v>
       </c>
       <c r="D243" t="n">
-        <v>10552</v>
+        <v>19681</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>103.88</v>
+        <v>84.63</v>
       </c>
       <c r="B244" t="n">
-        <v>48661</v>
+        <v>19543</v>
       </c>
       <c r="C244" t="n">
-        <v>101.31</v>
+        <v>71.7</v>
       </c>
       <c r="D244" t="n">
-        <v>11164</v>
+        <v>18845</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>68.73999999999999</v>
+        <v>84.91</v>
       </c>
       <c r="B245" t="n">
-        <v>23378</v>
+        <v>20107</v>
       </c>
       <c r="C245" t="n">
-        <v>70.88</v>
+        <v>63.34</v>
       </c>
       <c r="D245" t="n">
-        <v>11626</v>
+        <v>28473</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>41.82</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="B246" t="n">
-        <v>23743</v>
+        <v>20312</v>
       </c>
       <c r="C246" t="n">
-        <v>42.82</v>
+        <v>102.26</v>
       </c>
       <c r="D246" t="n">
-        <v>12954</v>
+        <v>11782</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>114.22</v>
+        <v>86</v>
       </c>
       <c r="B247" t="n">
-        <v>23265</v>
+        <v>20945</v>
       </c>
       <c r="C247" t="n">
-        <v>111.89</v>
+        <v>92.12</v>
       </c>
       <c r="D247" t="n">
-        <v>26187</v>
+        <v>13396</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>93.34999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="B248" t="n">
-        <v>31467</v>
+        <v>20560</v>
       </c>
       <c r="C248" t="n">
-        <v>92.11</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="D248" t="n">
-        <v>22754</v>
+        <v>16697</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>105.38</v>
+        <v>86.66</v>
       </c>
       <c r="B249" t="n">
-        <v>44686</v>
+        <v>19855</v>
       </c>
       <c r="C249" t="n">
-        <v>103.09</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="D249" t="n">
-        <v>17737</v>
+        <v>10909</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>92.56999999999999</v>
+        <v>87.02</v>
       </c>
       <c r="B250" t="n">
-        <v>25634</v>
+        <v>19870</v>
       </c>
       <c r="C250" t="n">
-        <v>90.56</v>
+        <v>98.84</v>
       </c>
       <c r="D250" t="n">
-        <v>25143</v>
+        <v>23279</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>87.09</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="B251" t="n">
-        <v>24798</v>
+        <v>20335</v>
       </c>
       <c r="C251" t="n">
-        <v>89.5</v>
+        <v>90.33</v>
       </c>
       <c r="D251" t="n">
-        <v>27361</v>
+        <v>16356</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>92.41</v>
+        <v>87.47</v>
       </c>
       <c r="B252" t="n">
-        <v>28004</v>
+        <v>20495</v>
       </c>
       <c r="C252" t="n">
-        <v>92.98</v>
+        <v>92.53</v>
       </c>
       <c r="D252" t="n">
-        <v>21958</v>
+        <v>25762</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>97.15000000000001</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="B253" t="n">
-        <v>37813</v>
+        <v>20401</v>
       </c>
       <c r="C253" t="n">
-        <v>97.11</v>
+        <v>107.54</v>
       </c>
       <c r="D253" t="n">
-        <v>27017</v>
+        <v>25029</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>109.76</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="B254" t="n">
-        <v>35334</v>
+        <v>20821</v>
       </c>
       <c r="C254" t="n">
-        <v>109.84</v>
+        <v>93.37</v>
       </c>
       <c r="D254" t="n">
-        <v>22656</v>
+        <v>24208</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>94.17</v>
+        <v>88.63</v>
       </c>
       <c r="B255" t="n">
-        <v>30927</v>
+        <v>21457</v>
       </c>
       <c r="C255" t="n">
-        <v>96.38</v>
+        <v>91.08</v>
       </c>
       <c r="D255" t="n">
-        <v>15241</v>
+        <v>13296</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>90.12</v>
+        <v>88.69</v>
       </c>
       <c r="B256" t="n">
-        <v>23566</v>
+        <v>20828</v>
       </c>
       <c r="C256" t="n">
-        <v>92.90000000000001</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="D256" t="n">
-        <v>24959</v>
+        <v>24172</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>109.33</v>
+        <v>88.95</v>
       </c>
       <c r="B257" t="n">
-        <v>34123</v>
+        <v>20027</v>
       </c>
       <c r="C257" t="n">
-        <v>104.87</v>
+        <v>99.25</v>
       </c>
       <c r="D257" t="n">
-        <v>26665</v>
+        <v>21127</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>176.58</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="B258" t="n">
-        <v>25359</v>
+        <v>20307</v>
       </c>
       <c r="C258" t="n">
-        <v>170.31</v>
+        <v>89.22</v>
       </c>
       <c r="D258" t="n">
-        <v>19760</v>
+        <v>21416</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>99.7</v>
+        <v>89.3</v>
       </c>
       <c r="B259" t="n">
-        <v>45393</v>
+        <v>21005</v>
       </c>
       <c r="C259" t="n">
-        <v>104.14</v>
+        <v>99.37</v>
       </c>
       <c r="D259" t="n">
-        <v>15317</v>
+        <v>21051</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>102.91</v>
+        <v>89.5</v>
       </c>
       <c r="B260" t="n">
-        <v>47317</v>
+        <v>21214</v>
       </c>
       <c r="C260" t="n">
-        <v>104.37</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="D260" t="n">
-        <v>27397</v>
+        <v>23515</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>91.05</v>
+        <v>90.22</v>
       </c>
       <c r="B261" t="n">
-        <v>24598</v>
+        <v>20702</v>
       </c>
       <c r="C261" t="n">
-        <v>87.98</v>
+        <v>101.55</v>
       </c>
       <c r="D261" t="n">
-        <v>19518</v>
+        <v>25450</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>102.15</v>
+        <v>90.27</v>
       </c>
       <c r="B262" t="n">
-        <v>49909</v>
+        <v>21387</v>
       </c>
       <c r="C262" t="n">
-        <v>103.72</v>
+        <v>113.93</v>
       </c>
       <c r="D262" t="n">
-        <v>27033</v>
+        <v>29798</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>15.94</v>
+        <v>90.42</v>
       </c>
       <c r="B263" t="n">
-        <v>21052</v>
+        <v>19818</v>
       </c>
       <c r="C263" t="n">
-        <v>15.11</v>
+        <v>97.36</v>
       </c>
       <c r="D263" t="n">
-        <v>17244</v>
+        <v>17086</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>98.73</v>
+        <v>90.67</v>
       </c>
       <c r="B264" t="n">
-        <v>42723</v>
+        <v>20472</v>
       </c>
       <c r="C264" t="n">
-        <v>101.5</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="D264" t="n">
-        <v>18314</v>
+        <v>23145</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>95.27</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="B265" t="n">
-        <v>33628</v>
+        <v>21133</v>
       </c>
       <c r="C265" t="n">
-        <v>97.40000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="D265" t="n">
-        <v>23851</v>
+        <v>27628</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>98.44</v>
+        <v>91.84</v>
       </c>
       <c r="B266" t="n">
-        <v>42585</v>
+        <v>21174</v>
       </c>
       <c r="C266" t="n">
-        <v>100.56</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="D266" t="n">
-        <v>10508</v>
+        <v>24773</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>94.09</v>
+        <v>92.02</v>
       </c>
       <c r="B267" t="n">
-        <v>28993</v>
+        <v>21295</v>
       </c>
       <c r="C267" t="n">
-        <v>92.86</v>
+        <v>91.53</v>
       </c>
       <c r="D267" t="n">
-        <v>26781</v>
+        <v>10718</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>8.74</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="B268" t="n">
-        <v>21255</v>
+        <v>21253</v>
       </c>
       <c r="C268" t="n">
-        <v>8.67</v>
+        <v>67.84</v>
       </c>
       <c r="D268" t="n">
-        <v>25691</v>
+        <v>16587</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>99.45</v>
+        <v>92.34</v>
       </c>
       <c r="B269" t="n">
-        <v>44655</v>
+        <v>21551</v>
       </c>
       <c r="C269" t="n">
-        <v>102.08</v>
+        <v>86.55</v>
       </c>
       <c r="D269" t="n">
-        <v>20977</v>
+        <v>14614</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>99.61</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="B270" t="n">
-        <v>47704</v>
+        <v>23685</v>
       </c>
       <c r="C270" t="n">
-        <v>97.72</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D270" t="n">
-        <v>16481</v>
+        <v>29847</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>105.22</v>
+        <v>92.98</v>
       </c>
       <c r="B271" t="n">
-        <v>45953</v>
+        <v>23277</v>
       </c>
       <c r="C271" t="n">
-        <v>103.23</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="D271" t="n">
-        <v>17241</v>
+        <v>17969</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>94.02</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="B272" t="n">
-        <v>30867</v>
+        <v>22637</v>
       </c>
       <c r="C272" t="n">
-        <v>94</v>
+        <v>96.94</v>
       </c>
       <c r="D272" t="n">
-        <v>28808</v>
+        <v>28584</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>109.43</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="B273" t="n">
-        <v>33140</v>
+        <v>23606</v>
       </c>
       <c r="C273" t="n">
-        <v>108.18</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="D273" t="n">
-        <v>24035</v>
+        <v>27749</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>111.85</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="B274" t="n">
-        <v>25938</v>
+        <v>24812</v>
       </c>
       <c r="C274" t="n">
-        <v>114.34</v>
+        <v>95.44</v>
       </c>
       <c r="D274" t="n">
-        <v>28982</v>
+        <v>20725</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>109.8</v>
+        <v>94.84</v>
       </c>
       <c r="B275" t="n">
-        <v>31472</v>
+        <v>24419</v>
       </c>
       <c r="C275" t="n">
-        <v>108.98</v>
+        <v>85.75</v>
       </c>
       <c r="D275" t="n">
-        <v>29231</v>
+        <v>12105</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>114.04</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="B276" t="n">
-        <v>25872</v>
+        <v>25450</v>
       </c>
       <c r="C276" t="n">
-        <v>110.34</v>
+        <v>112.01</v>
       </c>
       <c r="D276" t="n">
-        <v>23111</v>
+        <v>28408</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>113.71</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="B277" t="n">
-        <v>23496</v>
+        <v>25801</v>
       </c>
       <c r="C277" t="n">
-        <v>113.98</v>
+        <v>89.98</v>
       </c>
       <c r="D277" t="n">
-        <v>12534</v>
+        <v>21625</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>109.1</v>
+        <v>95.77</v>
       </c>
       <c r="B278" t="n">
-        <v>37381</v>
+        <v>27125</v>
       </c>
       <c r="C278" t="n">
-        <v>113.42</v>
+        <v>110.21</v>
       </c>
       <c r="D278" t="n">
-        <v>29347</v>
+        <v>23761</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>112.58</v>
+        <v>96.11</v>
       </c>
       <c r="B279" t="n">
-        <v>24334</v>
+        <v>26570</v>
       </c>
       <c r="C279" t="n">
-        <v>114.27</v>
+        <v>107.78</v>
       </c>
       <c r="D279" t="n">
-        <v>18439</v>
+        <v>12020</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>174.87</v>
+        <v>96.38</v>
       </c>
       <c r="B280" t="n">
-        <v>20917</v>
+        <v>28225</v>
       </c>
       <c r="C280" t="n">
-        <v>176.7</v>
+        <v>94.67</v>
       </c>
       <c r="D280" t="n">
-        <v>19368</v>
+        <v>23457</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>100.51</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="B281" t="n">
-        <v>46633</v>
+        <v>27778</v>
       </c>
       <c r="C281" t="n">
-        <v>97.53</v>
+        <v>88.7</v>
       </c>
       <c r="D281" t="n">
-        <v>28095</v>
+        <v>22064</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>106.51</v>
+        <v>96.78</v>
       </c>
       <c r="B282" t="n">
-        <v>43065</v>
+        <v>28307</v>
       </c>
       <c r="C282" t="n">
-        <v>106.88</v>
+        <v>114.46</v>
       </c>
       <c r="D282" t="n">
-        <v>25007</v>
+        <v>19083</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>105.06</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="B283" t="n">
-        <v>47258</v>
+        <v>29186</v>
       </c>
       <c r="C283" t="n">
-        <v>106.8</v>
+        <v>115.29</v>
       </c>
       <c r="D283" t="n">
-        <v>18786</v>
+        <v>13606</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>111.14</v>
+        <v>97.64</v>
       </c>
       <c r="B284" t="n">
-        <v>26692</v>
+        <v>30395</v>
       </c>
       <c r="C284" t="n">
-        <v>107.87</v>
+        <v>87.2</v>
       </c>
       <c r="D284" t="n">
-        <v>17285</v>
+        <v>25981</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>94.02</v>
+        <v>98.2</v>
       </c>
       <c r="B285" t="n">
-        <v>32108</v>
+        <v>31711</v>
       </c>
       <c r="C285" t="n">
-        <v>97.02</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="D285" t="n">
-        <v>29082</v>
+        <v>24116</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>93.41</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="B286" t="n">
-        <v>31124</v>
+        <v>31752</v>
       </c>
       <c r="C286" t="n">
-        <v>97.14</v>
+        <v>86.22</v>
       </c>
       <c r="D286" t="n">
-        <v>23077</v>
+        <v>17402</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>107.08</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="B287" t="n">
-        <v>41311</v>
+        <v>31434</v>
       </c>
       <c r="C287" t="n">
-        <v>110.89</v>
+        <v>103.34</v>
       </c>
       <c r="D287" t="n">
-        <v>20202</v>
+        <v>13309</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>97.18000000000001</v>
+        <v>99.28</v>
       </c>
       <c r="B288" t="n">
-        <v>38995</v>
+        <v>33326</v>
       </c>
       <c r="C288" t="n">
-        <v>95.54000000000001</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D288" t="n">
-        <v>12931</v>
+        <v>20114</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>90.02</v>
+        <v>99.28</v>
       </c>
       <c r="B289" t="n">
-        <v>25173</v>
+        <v>32700</v>
       </c>
       <c r="C289" t="n">
-        <v>90.33</v>
+        <v>121.7</v>
       </c>
       <c r="D289" t="n">
-        <v>14998</v>
+        <v>19741</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>107.99</v>
+        <v>100.05</v>
       </c>
       <c r="B290" t="n">
-        <v>39688</v>
+        <v>35432</v>
       </c>
       <c r="C290" t="n">
-        <v>105.52</v>
+        <v>131.21</v>
       </c>
       <c r="D290" t="n">
-        <v>25896</v>
+        <v>13469</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>78.36</v>
+        <v>100.67</v>
       </c>
       <c r="B291" t="n">
-        <v>24469</v>
+        <v>35663</v>
       </c>
       <c r="C291" t="n">
-        <v>80.2</v>
+        <v>85.98</v>
       </c>
       <c r="D291" t="n">
-        <v>12036</v>
+        <v>18455</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>43.7</v>
+        <v>100.7</v>
       </c>
       <c r="B292" t="n">
-        <v>26377</v>
+        <v>35706</v>
       </c>
       <c r="C292" t="n">
-        <v>43.11</v>
+        <v>92.8</v>
       </c>
       <c r="D292" t="n">
-        <v>27914</v>
+        <v>21247</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>101.26</v>
+        <v>100.93</v>
       </c>
       <c r="B293" t="n">
-        <v>45727</v>
+        <v>35224</v>
       </c>
       <c r="C293" t="n">
-        <v>98.91</v>
+        <v>119.98</v>
       </c>
       <c r="D293" t="n">
-        <v>11400</v>
+        <v>14679</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>102.87</v>
+        <v>101.63</v>
       </c>
       <c r="B294" t="n">
-        <v>45557</v>
+        <v>37104</v>
       </c>
       <c r="C294" t="n">
-        <v>105.36</v>
+        <v>101.91</v>
       </c>
       <c r="D294" t="n">
-        <v>13296</v>
+        <v>21019</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>108.44</v>
+        <v>101.92</v>
       </c>
       <c r="B295" t="n">
-        <v>36915</v>
+        <v>37335</v>
       </c>
       <c r="C295" t="n">
-        <v>109.66</v>
+        <v>120.54</v>
       </c>
       <c r="D295" t="n">
-        <v>22306</v>
+        <v>12829</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>113.92</v>
+        <v>102.29</v>
       </c>
       <c r="B296" t="n">
-        <v>22731</v>
+        <v>38462</v>
       </c>
       <c r="C296" t="n">
-        <v>111.69</v>
+        <v>104.33</v>
       </c>
       <c r="D296" t="n">
-        <v>19302</v>
+        <v>22866</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>106.77</v>
+        <v>103.71</v>
       </c>
       <c r="B297" t="n">
-        <v>43642</v>
+        <v>37518</v>
       </c>
       <c r="C297" t="n">
-        <v>106.82</v>
+        <v>98.77</v>
       </c>
       <c r="D297" t="n">
-        <v>12403</v>
+        <v>18502</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>130.03</v>
+        <v>103.92</v>
       </c>
       <c r="B298" t="n">
-        <v>21250</v>
+        <v>37734</v>
       </c>
       <c r="C298" t="n">
-        <v>130.39</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D298" t="n">
-        <v>19668</v>
+        <v>14209</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>95.20999999999999</v>
+        <v>104.77</v>
       </c>
       <c r="B299" t="n">
-        <v>37434</v>
+        <v>37712</v>
       </c>
       <c r="C299" t="n">
-        <v>95.84</v>
+        <v>104.78</v>
       </c>
       <c r="D299" t="n">
-        <v>20749</v>
+        <v>19357</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>90.81999999999999</v>
+        <v>104.91</v>
       </c>
       <c r="B300" t="n">
-        <v>24529</v>
+        <v>36809</v>
       </c>
       <c r="C300" t="n">
-        <v>87.67</v>
+        <v>109.25</v>
       </c>
       <c r="D300" t="n">
-        <v>20404</v>
+        <v>25257</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>99.40000000000001</v>
+        <v>105.01</v>
       </c>
       <c r="B301" t="n">
-        <v>43399</v>
+        <v>36277</v>
       </c>
       <c r="C301" t="n">
-        <v>95.48</v>
+        <v>117.69</v>
       </c>
       <c r="D301" t="n">
-        <v>13566</v>
+        <v>24480</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>99.66</v>
+        <v>106.06</v>
       </c>
       <c r="B302" t="n">
-        <v>45162</v>
+        <v>34334</v>
       </c>
       <c r="C302" t="n">
-        <v>100.51</v>
+        <v>106.58</v>
       </c>
       <c r="D302" t="n">
-        <v>14530</v>
+        <v>17516</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>102.55</v>
+        <v>106.33</v>
       </c>
       <c r="B303" t="n">
-        <v>47520</v>
+        <v>35722</v>
       </c>
       <c r="C303" t="n">
-        <v>99.61</v>
+        <v>107.58</v>
       </c>
       <c r="D303" t="n">
-        <v>23679</v>
+        <v>22184</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>113.88</v>
+        <v>106.72</v>
       </c>
       <c r="B304" t="n">
-        <v>24601</v>
+        <v>34385</v>
       </c>
       <c r="C304" t="n">
-        <v>115.55</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D304" t="n">
-        <v>28008</v>
+        <v>29742</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>91.72</v>
+        <v>106.92</v>
       </c>
       <c r="B305" t="n">
-        <v>24901</v>
+        <v>32752</v>
       </c>
       <c r="C305" t="n">
-        <v>94.27</v>
+        <v>87.73</v>
       </c>
       <c r="D305" t="n">
-        <v>26663</v>
+        <v>29687</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>101.99</v>
+        <v>107.02</v>
       </c>
       <c r="B306" t="n">
-        <v>45319</v>
+        <v>32564</v>
       </c>
       <c r="C306" t="n">
-        <v>104.78</v>
+        <v>91.47</v>
       </c>
       <c r="D306" t="n">
-        <v>20604</v>
+        <v>28596</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>105.31</v>
+        <v>107.84</v>
       </c>
       <c r="B307" t="n">
-        <v>44463</v>
+        <v>31494</v>
       </c>
       <c r="C307" t="n">
-        <v>104.12</v>
+        <v>106.82</v>
       </c>
       <c r="D307" t="n">
-        <v>16416</v>
+        <v>16138</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>54.84</v>
+        <v>108.34</v>
       </c>
       <c r="B308" t="n">
-        <v>23918</v>
+        <v>29399</v>
       </c>
       <c r="C308" t="n">
-        <v>53.13</v>
+        <v>99.05</v>
       </c>
       <c r="D308" t="n">
-        <v>12585</v>
+        <v>15433</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>97.44</v>
+        <v>108.88</v>
       </c>
       <c r="B309" t="n">
-        <v>40472</v>
+        <v>29084</v>
       </c>
       <c r="C309" t="n">
-        <v>101.45</v>
+        <v>106.51</v>
       </c>
       <c r="D309" t="n">
-        <v>11932</v>
+        <v>16297</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>93.34</v>
+        <v>109.51</v>
       </c>
       <c r="B310" t="n">
-        <v>27845</v>
+        <v>27726</v>
       </c>
       <c r="C310" t="n">
-        <v>97.06</v>
+        <v>122.72</v>
       </c>
       <c r="D310" t="n">
-        <v>19159</v>
+        <v>26824</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>113.69</v>
+        <v>109.9</v>
       </c>
       <c r="B311" t="n">
-        <v>25067</v>
+        <v>26551</v>
       </c>
       <c r="C311" t="n">
-        <v>117.02</v>
+        <v>119.44</v>
       </c>
       <c r="D311" t="n">
-        <v>13801</v>
+        <v>17232</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>99</v>
+        <v>110.12</v>
       </c>
       <c r="B312" t="n">
-        <v>43915</v>
+        <v>26184</v>
       </c>
       <c r="C312" t="n">
-        <v>95.31999999999999</v>
+        <v>121.11</v>
       </c>
       <c r="D312" t="n">
-        <v>16516</v>
+        <v>19138</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>92.63</v>
+        <v>110.21</v>
       </c>
       <c r="B313" t="n">
-        <v>27661</v>
+        <v>25935</v>
       </c>
       <c r="C313" t="n">
-        <v>92.16</v>
+        <v>95.66</v>
       </c>
       <c r="D313" t="n">
-        <v>25088</v>
+        <v>20420</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>94.19</v>
+        <v>110.22</v>
       </c>
       <c r="B314" t="n">
-        <v>32368</v>
+        <v>26195</v>
       </c>
       <c r="C314" t="n">
-        <v>97.40000000000001</v>
+        <v>86.06</v>
       </c>
       <c r="D314" t="n">
-        <v>14518</v>
+        <v>14614</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>112.28</v>
+        <v>110.7</v>
       </c>
       <c r="B315" t="n">
-        <v>24526</v>
+        <v>25107</v>
       </c>
       <c r="C315" t="n">
-        <v>114.5</v>
+        <v>113.53</v>
       </c>
       <c r="D315" t="n">
-        <v>17088</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>73.62</v>
+        <v>111.1</v>
       </c>
       <c r="B316" t="n">
-        <v>26118</v>
+        <v>23927</v>
       </c>
       <c r="C316" t="n">
-        <v>72.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D316" t="n">
-        <v>20736</v>
+        <v>21999</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>104.69</v>
+        <v>111.13</v>
       </c>
       <c r="B317" t="n">
-        <v>44013</v>
+        <v>23922</v>
       </c>
       <c r="C317" t="n">
-        <v>100.04</v>
+        <v>102.53</v>
       </c>
       <c r="D317" t="n">
-        <v>25512</v>
+        <v>15212</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>90.22</v>
+        <v>111.26</v>
       </c>
       <c r="B318" t="n">
-        <v>24237</v>
+        <v>24403</v>
       </c>
       <c r="C318" t="n">
-        <v>89.64</v>
+        <v>114.79</v>
       </c>
       <c r="D318" t="n">
-        <v>10430</v>
+        <v>26454</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>105.07</v>
+        <v>111.62</v>
       </c>
       <c r="B319" t="n">
-        <v>46967</v>
+        <v>24533</v>
       </c>
       <c r="C319" t="n">
-        <v>108.22</v>
+        <v>105.8</v>
       </c>
       <c r="D319" t="n">
-        <v>27102</v>
+        <v>26425</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>109</v>
+        <v>111.73</v>
       </c>
       <c r="B320" t="n">
-        <v>35750</v>
+        <v>23296</v>
       </c>
       <c r="C320" t="n">
-        <v>109.75</v>
+        <v>120.98</v>
       </c>
       <c r="D320" t="n">
-        <v>25715</v>
+        <v>28081</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>100.51</v>
+        <v>111.82</v>
       </c>
       <c r="B321" t="n">
-        <v>45724</v>
+        <v>24326</v>
       </c>
       <c r="C321" t="n">
-        <v>104.43</v>
+        <v>122.11</v>
       </c>
       <c r="D321" t="n">
-        <v>26347</v>
+        <v>24753</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>100.19</v>
+        <v>111.84</v>
       </c>
       <c r="B322" t="n">
-        <v>42798</v>
+        <v>23887</v>
       </c>
       <c r="C322" t="n">
-        <v>97.17</v>
+        <v>104.38</v>
       </c>
       <c r="D322" t="n">
-        <v>28134</v>
+        <v>12332</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>56.88</v>
+        <v>112.12</v>
       </c>
       <c r="B323" t="n">
-        <v>22922</v>
+        <v>21972</v>
       </c>
       <c r="C323" t="n">
-        <v>55.11</v>
+        <v>139.15</v>
       </c>
       <c r="D323" t="n">
-        <v>23130</v>
+        <v>29928</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>105.29</v>
+        <v>112.13</v>
       </c>
       <c r="B324" t="n">
-        <v>44804</v>
+        <v>23983</v>
       </c>
       <c r="C324" t="n">
-        <v>106.32</v>
+        <v>110.81</v>
       </c>
       <c r="D324" t="n">
-        <v>19841</v>
+        <v>10247</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>102.45</v>
+        <v>112.25</v>
       </c>
       <c r="B325" t="n">
-        <v>46947</v>
+        <v>22920</v>
       </c>
       <c r="C325" t="n">
-        <v>101.66</v>
+        <v>116.89</v>
       </c>
       <c r="D325" t="n">
-        <v>25632</v>
+        <v>13358</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>102.44</v>
+        <v>112.31</v>
       </c>
       <c r="B326" t="n">
-        <v>47462</v>
+        <v>22978</v>
       </c>
       <c r="C326" t="n">
-        <v>105.76</v>
+        <v>112.51</v>
       </c>
       <c r="D326" t="n">
-        <v>25019</v>
+        <v>28080</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>105.76</v>
+        <v>113.34</v>
       </c>
       <c r="B327" t="n">
-        <v>44198</v>
+        <v>21951</v>
       </c>
       <c r="C327" t="n">
-        <v>104.09</v>
+        <v>122.24</v>
       </c>
       <c r="D327" t="n">
-        <v>13929</v>
+        <v>16455</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>100.71</v>
+        <v>114.86</v>
       </c>
       <c r="B328" t="n">
-        <v>44663</v>
+        <v>19774</v>
       </c>
       <c r="C328" t="n">
-        <v>99.23999999999999</v>
+        <v>129.46</v>
       </c>
       <c r="D328" t="n">
-        <v>10193</v>
+        <v>23490</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>113.01</v>
+        <v>114.9</v>
       </c>
       <c r="B329" t="n">
-        <v>27510</v>
+        <v>20295</v>
       </c>
       <c r="C329" t="n">
-        <v>109.47</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="D329" t="n">
-        <v>19860</v>
+        <v>22267</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>91.68000000000001</v>
+        <v>115.14</v>
       </c>
       <c r="B330" t="n">
-        <v>25289</v>
+        <v>19816</v>
       </c>
       <c r="C330" t="n">
-        <v>93.78</v>
+        <v>130.45</v>
       </c>
       <c r="D330" t="n">
-        <v>24898</v>
+        <v>24530</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>58.77</v>
+        <v>115.21</v>
       </c>
       <c r="B331" t="n">
-        <v>21874</v>
+        <v>20741</v>
       </c>
       <c r="C331" t="n">
-        <v>58.33</v>
+        <v>115.03</v>
       </c>
       <c r="D331" t="n">
-        <v>28465</v>
+        <v>10838</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>113.48</v>
+        <v>115.86</v>
       </c>
       <c r="B332" t="n">
-        <v>23222</v>
+        <v>21229</v>
       </c>
       <c r="C332" t="n">
-        <v>110.43</v>
+        <v>109.34</v>
       </c>
       <c r="D332" t="n">
-        <v>25287</v>
+        <v>16955</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>114.12</v>
+        <v>116.45</v>
       </c>
       <c r="B333" t="n">
-        <v>25792</v>
+        <v>19795</v>
       </c>
       <c r="C333" t="n">
-        <v>118.32</v>
+        <v>137.27</v>
       </c>
       <c r="D333" t="n">
-        <v>23207</v>
+        <v>25197</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>97.29000000000001</v>
+        <v>117.36</v>
       </c>
       <c r="B334" t="n">
-        <v>38184</v>
+        <v>21685</v>
       </c>
       <c r="C334" t="n">
-        <v>94.20999999999999</v>
+        <v>106.82</v>
       </c>
       <c r="D334" t="n">
-        <v>12284</v>
+        <v>19076</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>158.55</v>
+        <v>118.03</v>
       </c>
       <c r="B335" t="n">
-        <v>19877</v>
+        <v>19545</v>
       </c>
       <c r="C335" t="n">
-        <v>165.91</v>
+        <v>116.06</v>
       </c>
       <c r="D335" t="n">
-        <v>12400</v>
+        <v>10753</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>111.34</v>
+        <v>118.6</v>
       </c>
       <c r="B336" t="n">
-        <v>29497</v>
+        <v>19870</v>
       </c>
       <c r="C336" t="n">
-        <v>114.2</v>
+        <v>128.8</v>
       </c>
       <c r="D336" t="n">
-        <v>29681</v>
+        <v>10749</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>97.72</v>
+        <v>118.6</v>
       </c>
       <c r="B337" t="n">
-        <v>41104</v>
+        <v>20829</v>
       </c>
       <c r="C337" t="n">
-        <v>100.8</v>
+        <v>108.73</v>
       </c>
       <c r="D337" t="n">
-        <v>17857</v>
+        <v>17582</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>110.48</v>
+        <v>118.62</v>
       </c>
       <c r="B338" t="n">
-        <v>31788</v>
+        <v>20932</v>
       </c>
       <c r="C338" t="n">
-        <v>113.02</v>
+        <v>108.12</v>
       </c>
       <c r="D338" t="n">
-        <v>28813</v>
+        <v>11227</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>113.8</v>
+        <v>118.69</v>
       </c>
       <c r="B339" t="n">
-        <v>22188</v>
+        <v>20972</v>
       </c>
       <c r="C339" t="n">
-        <v>115.13</v>
+        <v>135.92</v>
       </c>
       <c r="D339" t="n">
-        <v>26300</v>
+        <v>25902</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>96.19</v>
+        <v>118.72</v>
       </c>
       <c r="B340" t="n">
-        <v>36401</v>
+        <v>19539</v>
       </c>
       <c r="C340" t="n">
-        <v>96.01000000000001</v>
+        <v>117.56</v>
       </c>
       <c r="D340" t="n">
-        <v>27035</v>
+        <v>29395</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>115.28</v>
+        <v>120.03</v>
       </c>
       <c r="B341" t="n">
-        <v>25284</v>
+        <v>19803</v>
       </c>
       <c r="C341" t="n">
-        <v>114.76</v>
+        <v>118.86</v>
       </c>
       <c r="D341" t="n">
-        <v>27662</v>
+        <v>25017</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>104.27</v>
+        <v>120.21</v>
       </c>
       <c r="B342" t="n">
-        <v>45150</v>
+        <v>19632</v>
       </c>
       <c r="C342" t="n">
-        <v>106.2</v>
+        <v>145.74</v>
       </c>
       <c r="D342" t="n">
-        <v>27548</v>
+        <v>24448</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>101.06</v>
+        <v>120.54</v>
       </c>
       <c r="B343" t="n">
-        <v>45408</v>
+        <v>20225</v>
       </c>
       <c r="C343" t="n">
-        <v>105.62</v>
+        <v>121.36</v>
       </c>
       <c r="D343" t="n">
-        <v>28159</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>103.16</v>
+        <v>120.97</v>
       </c>
       <c r="B344" t="n">
-        <v>44066</v>
+        <v>19448</v>
       </c>
       <c r="C344" t="n">
-        <v>103.05</v>
+        <v>129.66</v>
       </c>
       <c r="D344" t="n">
-        <v>29599</v>
+        <v>10159</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>97.34999999999999</v>
+        <v>121.01</v>
       </c>
       <c r="B345" t="n">
-        <v>38724</v>
+        <v>19008</v>
       </c>
       <c r="C345" t="n">
-        <v>95.5</v>
+        <v>131.13</v>
       </c>
       <c r="D345" t="n">
-        <v>16091</v>
+        <v>27797</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>105.18</v>
+        <v>121.65</v>
       </c>
       <c r="B346" t="n">
-        <v>43412</v>
+        <v>22305</v>
       </c>
       <c r="C346" t="n">
-        <v>109.35</v>
+        <v>110.87</v>
       </c>
       <c r="D346" t="n">
-        <v>21464</v>
+        <v>23550</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>59.33</v>
+        <v>121.81</v>
       </c>
       <c r="B347" t="n">
-        <v>25391</v>
+        <v>21473</v>
       </c>
       <c r="C347" t="n">
-        <v>62.21</v>
+        <v>114.95</v>
       </c>
       <c r="D347" t="n">
-        <v>10695</v>
+        <v>20222</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>93.62</v>
+        <v>121.92</v>
       </c>
       <c r="B348" t="n">
-        <v>31157</v>
+        <v>19853</v>
       </c>
       <c r="C348" t="n">
-        <v>91.7</v>
+        <v>121.79</v>
       </c>
       <c r="D348" t="n">
-        <v>15684</v>
+        <v>16371</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>113.08</v>
+        <v>121.96</v>
       </c>
       <c r="B349" t="n">
-        <v>24819</v>
+        <v>19153</v>
       </c>
       <c r="C349" t="n">
-        <v>109.86</v>
+        <v>119.51</v>
       </c>
       <c r="D349" t="n">
-        <v>28159</v>
+        <v>15884</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>90.43000000000001</v>
+        <v>122.56</v>
       </c>
       <c r="B350" t="n">
-        <v>25138</v>
+        <v>18921</v>
       </c>
       <c r="C350" t="n">
-        <v>93.56</v>
+        <v>126.08</v>
       </c>
       <c r="D350" t="n">
-        <v>21059</v>
+        <v>14754</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>94.61</v>
+        <v>122.67</v>
       </c>
       <c r="B351" t="n">
-        <v>32728</v>
+        <v>20049</v>
       </c>
       <c r="C351" t="n">
-        <v>98.69</v>
+        <v>119.84</v>
       </c>
       <c r="D351" t="n">
-        <v>27043</v>
+        <v>10329</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>102.85</v>
+        <v>122.94</v>
       </c>
       <c r="B352" t="n">
-        <v>47098</v>
+        <v>21396</v>
       </c>
       <c r="C352" t="n">
-        <v>100.28</v>
+        <v>132.15</v>
       </c>
       <c r="D352" t="n">
-        <v>12106</v>
+        <v>23942</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>97.63</v>
+        <v>123.99</v>
       </c>
       <c r="B353" t="n">
-        <v>40703</v>
+        <v>20900</v>
       </c>
       <c r="C353" t="n">
-        <v>96.12</v>
+        <v>102.76</v>
       </c>
       <c r="D353" t="n">
-        <v>12477</v>
+        <v>17488</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>100.31</v>
+        <v>124.29</v>
       </c>
       <c r="B354" t="n">
-        <v>44513</v>
+        <v>19960</v>
       </c>
       <c r="C354" t="n">
-        <v>97.33</v>
+        <v>112.38</v>
       </c>
       <c r="D354" t="n">
-        <v>22264</v>
+        <v>19179</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>104.19</v>
+        <v>124.81</v>
       </c>
       <c r="B355" t="n">
-        <v>47972</v>
+        <v>19044</v>
       </c>
       <c r="C355" t="n">
-        <v>106.06</v>
+        <v>100.06</v>
       </c>
       <c r="D355" t="n">
-        <v>22781</v>
+        <v>28140</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>71.64</v>
+        <v>124.83</v>
       </c>
       <c r="B356" t="n">
-        <v>24138</v>
+        <v>20890</v>
       </c>
       <c r="C356" t="n">
-        <v>73.36</v>
+        <v>120.41</v>
       </c>
       <c r="D356" t="n">
-        <v>15262</v>
+        <v>16422</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>114.78</v>
+        <v>124.85</v>
       </c>
       <c r="B357" t="n">
-        <v>22324</v>
+        <v>18738</v>
       </c>
       <c r="C357" t="n">
-        <v>115.85</v>
+        <v>119.39</v>
       </c>
       <c r="D357" t="n">
-        <v>23690</v>
+        <v>16705</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>92.72</v>
+        <v>125</v>
       </c>
       <c r="B358" t="n">
-        <v>28829</v>
+        <v>20810</v>
       </c>
       <c r="C358" t="n">
-        <v>89.58</v>
+        <v>123.31</v>
       </c>
       <c r="D358" t="n">
-        <v>15404</v>
+        <v>28910</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>102.73</v>
+        <v>125.53</v>
       </c>
       <c r="B359" t="n">
-        <v>49063</v>
+        <v>17685</v>
       </c>
       <c r="C359" t="n">
-        <v>100.31</v>
+        <v>110.56</v>
       </c>
       <c r="D359" t="n">
-        <v>14854</v>
+        <v>25888</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>93.66</v>
+        <v>125.81</v>
       </c>
       <c r="B360" t="n">
-        <v>32539</v>
+        <v>19835</v>
       </c>
       <c r="C360" t="n">
-        <v>93.25</v>
+        <v>119.11</v>
       </c>
       <c r="D360" t="n">
-        <v>17563</v>
+        <v>19659</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>95.02</v>
+        <v>127.78</v>
       </c>
       <c r="B361" t="n">
-        <v>33552</v>
+        <v>21705</v>
       </c>
       <c r="C361" t="n">
-        <v>91.47</v>
+        <v>135.5</v>
       </c>
       <c r="D361" t="n">
-        <v>12634</v>
+        <v>17573</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>101.03</v>
+        <v>128.32</v>
       </c>
       <c r="B362" t="n">
-        <v>44132</v>
+        <v>20147</v>
       </c>
       <c r="C362" t="n">
-        <v>97.98</v>
+        <v>130.86</v>
       </c>
       <c r="D362" t="n">
-        <v>23112</v>
+        <v>18420</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>34.15</v>
+        <v>128.34</v>
       </c>
       <c r="B363" t="n">
-        <v>24528</v>
+        <v>21240</v>
       </c>
       <c r="C363" t="n">
-        <v>34.68</v>
+        <v>148.53</v>
       </c>
       <c r="D363" t="n">
-        <v>21886</v>
+        <v>12769</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>62.19</v>
+        <v>128.5</v>
       </c>
       <c r="B364" t="n">
-        <v>25005</v>
+        <v>21586</v>
       </c>
       <c r="C364" t="n">
-        <v>63.91</v>
+        <v>111.71</v>
       </c>
       <c r="D364" t="n">
-        <v>21973</v>
+        <v>15001</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>105.19</v>
+        <v>128.56</v>
       </c>
       <c r="B365" t="n">
-        <v>44728</v>
+        <v>21037</v>
       </c>
       <c r="C365" t="n">
-        <v>109.69</v>
+        <v>127.15</v>
       </c>
       <c r="D365" t="n">
-        <v>23106</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>113.26</v>
+        <v>129.25</v>
       </c>
       <c r="B366" t="n">
-        <v>25760</v>
+        <v>19625</v>
       </c>
       <c r="C366" t="n">
-        <v>112.46</v>
+        <v>108.32</v>
       </c>
       <c r="D366" t="n">
-        <v>27139</v>
+        <v>21772</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>92.51000000000001</v>
+        <v>129.29</v>
       </c>
       <c r="B367" t="n">
-        <v>25557</v>
+        <v>20275</v>
       </c>
       <c r="C367" t="n">
-        <v>96.44</v>
+        <v>106.15</v>
       </c>
       <c r="D367" t="n">
-        <v>28810</v>
+        <v>27047</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>154.45</v>
+        <v>130.14</v>
       </c>
       <c r="B368" t="n">
-        <v>25034</v>
+        <v>18949</v>
       </c>
       <c r="C368" t="n">
-        <v>157.92</v>
+        <v>153.29</v>
       </c>
       <c r="D368" t="n">
-        <v>27472</v>
+        <v>27251</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>102.54</v>
+        <v>132.06</v>
       </c>
       <c r="B369" t="n">
-        <v>46149</v>
+        <v>19166</v>
       </c>
       <c r="C369" t="n">
-        <v>106.94</v>
+        <v>117.99</v>
       </c>
       <c r="D369" t="n">
-        <v>24446</v>
+        <v>19443</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>90.37</v>
+        <v>132.43</v>
       </c>
       <c r="B370" t="n">
-        <v>21158</v>
+        <v>18767</v>
       </c>
       <c r="C370" t="n">
-        <v>87.41</v>
+        <v>137.86</v>
       </c>
       <c r="D370" t="n">
-        <v>23596</v>
+        <v>11459</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>90.5</v>
+        <v>132.83</v>
       </c>
       <c r="B371" t="n">
-        <v>26199</v>
+        <v>20750</v>
       </c>
       <c r="C371" t="n">
-        <v>89.56</v>
+        <v>166.57</v>
       </c>
       <c r="D371" t="n">
-        <v>29291</v>
+        <v>28750</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>109.92</v>
+        <v>132.95</v>
       </c>
       <c r="B372" t="n">
-        <v>31472</v>
+        <v>20140</v>
       </c>
       <c r="C372" t="n">
-        <v>113.25</v>
+        <v>119.61</v>
       </c>
       <c r="D372" t="n">
-        <v>12123</v>
+        <v>18711</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>114.53</v>
+        <v>133.59</v>
       </c>
       <c r="B373" t="n">
-        <v>25872</v>
+        <v>17632</v>
       </c>
       <c r="C373" t="n">
-        <v>114.2</v>
+        <v>137.41</v>
       </c>
       <c r="D373" t="n">
-        <v>23829</v>
+        <v>23657</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>99.83</v>
+        <v>133.81</v>
       </c>
       <c r="B374" t="n">
-        <v>43526</v>
+        <v>19592</v>
       </c>
       <c r="C374" t="n">
-        <v>100.03</v>
+        <v>112.91</v>
       </c>
       <c r="D374" t="n">
-        <v>12543</v>
+        <v>21546</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>103.86</v>
+        <v>133.86</v>
       </c>
       <c r="B375" t="n">
-        <v>46087</v>
+        <v>17583</v>
       </c>
       <c r="C375" t="n">
-        <v>103.23</v>
+        <v>124.49</v>
       </c>
       <c r="D375" t="n">
-        <v>14271</v>
+        <v>29834</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>105.72</v>
+        <v>134.08</v>
       </c>
       <c r="B376" t="n">
-        <v>45112</v>
+        <v>18803</v>
       </c>
       <c r="C376" t="n">
-        <v>103.36</v>
+        <v>164.19</v>
       </c>
       <c r="D376" t="n">
-        <v>12450</v>
+        <v>15141</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>98.72</v>
+        <v>134.84</v>
       </c>
       <c r="B377" t="n">
-        <v>43830</v>
+        <v>18873</v>
       </c>
       <c r="C377" t="n">
-        <v>102.09</v>
+        <v>158.74</v>
       </c>
       <c r="D377" t="n">
-        <v>26620</v>
+        <v>28268</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>178.05</v>
+        <v>135.44</v>
       </c>
       <c r="B378" t="n">
-        <v>23182</v>
+        <v>22591</v>
       </c>
       <c r="C378" t="n">
-        <v>171.58</v>
+        <v>135.65</v>
       </c>
       <c r="D378" t="n">
-        <v>11503</v>
+        <v>17817</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>111.83</v>
+        <v>135.84</v>
       </c>
       <c r="B379" t="n">
-        <v>27058</v>
+        <v>17940</v>
       </c>
       <c r="C379" t="n">
-        <v>113.73</v>
+        <v>125.06</v>
       </c>
       <c r="D379" t="n">
-        <v>15648</v>
+        <v>26540</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>176.14</v>
+        <v>136.43</v>
       </c>
       <c r="B380" t="n">
-        <v>19322</v>
+        <v>19253</v>
       </c>
       <c r="C380" t="n">
-        <v>174.21</v>
+        <v>118.2</v>
       </c>
       <c r="D380" t="n">
-        <v>18226</v>
+        <v>22487</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>90.87</v>
+        <v>136.91</v>
       </c>
       <c r="B381" t="n">
-        <v>24218</v>
+        <v>19117</v>
       </c>
       <c r="C381" t="n">
-        <v>87.18000000000001</v>
+        <v>133.16</v>
       </c>
       <c r="D381" t="n">
-        <v>19646</v>
+        <v>24413</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>137.49</v>
+        <v>137.09</v>
       </c>
       <c r="B382" t="n">
-        <v>26619</v>
+        <v>22025</v>
       </c>
       <c r="C382" t="n">
-        <v>136.17</v>
+        <v>115.46</v>
       </c>
       <c r="D382" t="n">
-        <v>12066</v>
+        <v>25579</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>106.6</v>
+        <v>137.22</v>
       </c>
       <c r="B383" t="n">
-        <v>42901</v>
+        <v>20827</v>
       </c>
       <c r="C383" t="n">
-        <v>105.84</v>
+        <v>117.89</v>
       </c>
       <c r="D383" t="n">
-        <v>12223</v>
+        <v>13416</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>102.19</v>
+        <v>137.31</v>
       </c>
       <c r="B384" t="n">
-        <v>46173</v>
+        <v>20515</v>
       </c>
       <c r="C384" t="n">
-        <v>105.12</v>
+        <v>112.32</v>
       </c>
       <c r="D384" t="n">
-        <v>10279</v>
+        <v>17954</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>105.32</v>
+        <v>137.71</v>
       </c>
       <c r="B385" t="n">
-        <v>42336</v>
+        <v>19675</v>
       </c>
       <c r="C385" t="n">
-        <v>108.75</v>
+        <v>156.08</v>
       </c>
       <c r="D385" t="n">
-        <v>21517</v>
+        <v>23503</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>97.52</v>
+        <v>137.78</v>
       </c>
       <c r="B386" t="n">
-        <v>40448</v>
+        <v>15822</v>
       </c>
       <c r="C386" t="n">
-        <v>98.7</v>
+        <v>150.12</v>
       </c>
       <c r="D386" t="n">
-        <v>23722</v>
+        <v>27976</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>176.64</v>
+        <v>137.85</v>
       </c>
       <c r="B387" t="n">
-        <v>21806</v>
+        <v>21380</v>
       </c>
       <c r="C387" t="n">
-        <v>179.11</v>
+        <v>141.87</v>
       </c>
       <c r="D387" t="n">
-        <v>11047</v>
+        <v>15333</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>113.7</v>
+        <v>138.71</v>
       </c>
       <c r="B388" t="n">
-        <v>24838</v>
+        <v>19567</v>
       </c>
       <c r="C388" t="n">
-        <v>116.99</v>
+        <v>158.35</v>
       </c>
       <c r="D388" t="n">
-        <v>11733</v>
+        <v>28093</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>94.56999999999999</v>
+        <v>138.72</v>
       </c>
       <c r="B389" t="n">
-        <v>31042</v>
+        <v>18529</v>
       </c>
       <c r="C389" t="n">
-        <v>93.34</v>
+        <v>116.81</v>
       </c>
       <c r="D389" t="n">
-        <v>23072</v>
+        <v>14024</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>110.52</v>
+        <v>138.86</v>
       </c>
       <c r="B390" t="n">
-        <v>30143</v>
+        <v>16415</v>
       </c>
       <c r="C390" t="n">
-        <v>114.13</v>
+        <v>145.42</v>
       </c>
       <c r="D390" t="n">
-        <v>23639</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>90.29000000000001</v>
+        <v>139</v>
       </c>
       <c r="B391" t="n">
-        <v>23962</v>
+        <v>19072</v>
       </c>
       <c r="C391" t="n">
-        <v>89.06999999999999</v>
+        <v>167.86</v>
       </c>
       <c r="D391" t="n">
-        <v>29861</v>
+        <v>24690</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>106.18</v>
+        <v>139.52</v>
       </c>
       <c r="B392" t="n">
-        <v>42708</v>
+        <v>19141</v>
       </c>
       <c r="C392" t="n">
-        <v>103.61</v>
+        <v>136.98</v>
       </c>
       <c r="D392" t="n">
-        <v>13357</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>45.8</v>
+        <v>139.85</v>
       </c>
       <c r="B393" t="n">
-        <v>23334</v>
+        <v>18517</v>
       </c>
       <c r="C393" t="n">
-        <v>44.74</v>
+        <v>161.72</v>
       </c>
       <c r="D393" t="n">
-        <v>26238</v>
+        <v>21824</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>95.48999999999999</v>
+        <v>140.95</v>
       </c>
       <c r="B394" t="n">
-        <v>32724</v>
+        <v>20479</v>
       </c>
       <c r="C394" t="n">
-        <v>93.95</v>
+        <v>137.71</v>
       </c>
       <c r="D394" t="n">
-        <v>13533</v>
+        <v>25384</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>92.59</v>
+        <v>141.91</v>
       </c>
       <c r="B395" t="n">
-        <v>25643</v>
+        <v>21416</v>
       </c>
       <c r="C395" t="n">
-        <v>94.81</v>
+        <v>110.71</v>
       </c>
       <c r="D395" t="n">
-        <v>14218</v>
+        <v>15675</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>114.92</v>
+        <v>142.4</v>
       </c>
       <c r="B396" t="n">
-        <v>23909</v>
+        <v>20001</v>
       </c>
       <c r="C396" t="n">
-        <v>113.2</v>
+        <v>143.47</v>
       </c>
       <c r="D396" t="n">
-        <v>15998</v>
+        <v>14253</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>103.11</v>
+        <v>142.4</v>
       </c>
       <c r="B397" t="n">
-        <v>49245</v>
+        <v>19907</v>
       </c>
       <c r="C397" t="n">
-        <v>101.23</v>
+        <v>141.07</v>
       </c>
       <c r="D397" t="n">
-        <v>14475</v>
+        <v>29386</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>43.9</v>
+        <v>142.85</v>
       </c>
       <c r="B398" t="n">
-        <v>25239</v>
+        <v>19223</v>
       </c>
       <c r="C398" t="n">
-        <v>42.18</v>
+        <v>150.29</v>
       </c>
       <c r="D398" t="n">
-        <v>16064</v>
+        <v>13029</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>155.4</v>
+        <v>143.08</v>
       </c>
       <c r="B399" t="n">
-        <v>24470</v>
+        <v>17595</v>
       </c>
       <c r="C399" t="n">
-        <v>155.03</v>
+        <v>130.59</v>
       </c>
       <c r="D399" t="n">
-        <v>10400</v>
+        <v>10338</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>107.93</v>
+        <v>143.71</v>
       </c>
       <c r="B400" t="n">
-        <v>40583</v>
+        <v>19445</v>
       </c>
       <c r="C400" t="n">
-        <v>111.68</v>
+        <v>162.93</v>
       </c>
       <c r="D400" t="n">
-        <v>21523</v>
+        <v>18668</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>91.92</v>
+        <v>144.33</v>
       </c>
       <c r="B401" t="n">
-        <v>25761</v>
+        <v>20279</v>
       </c>
       <c r="C401" t="n">
-        <v>90.95999999999999</v>
+        <v>126.12</v>
       </c>
       <c r="D401" t="n">
-        <v>23236</v>
+        <v>11614</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>58.35</v>
+        <v>144.48</v>
       </c>
       <c r="B402" t="n">
-        <v>25683</v>
+        <v>20302</v>
       </c>
       <c r="C402" t="n">
-        <v>57.36</v>
+        <v>157.7</v>
       </c>
       <c r="D402" t="n">
-        <v>23152</v>
+        <v>14695</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>111.57</v>
+        <v>145.68</v>
       </c>
       <c r="B403" t="n">
-        <v>27328</v>
+        <v>19223</v>
       </c>
       <c r="C403" t="n">
-        <v>116.08</v>
+        <v>118.68</v>
       </c>
       <c r="D403" t="n">
-        <v>13074</v>
+        <v>18775</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>90.95</v>
+        <v>145.9</v>
       </c>
       <c r="B404" t="n">
-        <v>24670</v>
+        <v>20587</v>
       </c>
       <c r="C404" t="n">
-        <v>87.87</v>
+        <v>153.85</v>
       </c>
       <c r="D404" t="n">
-        <v>26762</v>
+        <v>11685</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>93.63</v>
+        <v>146.01</v>
       </c>
       <c r="B405" t="n">
-        <v>30820</v>
+        <v>21197</v>
       </c>
       <c r="C405" t="n">
-        <v>90.84999999999999</v>
+        <v>153.24</v>
       </c>
       <c r="D405" t="n">
-        <v>26647</v>
+        <v>26511</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>108.18</v>
+        <v>146.04</v>
       </c>
       <c r="B406" t="n">
-        <v>39067</v>
+        <v>20162</v>
       </c>
       <c r="C406" t="n">
-        <v>107.1</v>
+        <v>179.01</v>
       </c>
       <c r="D406" t="n">
-        <v>10566</v>
+        <v>13130</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>93.66</v>
+        <v>146.85</v>
       </c>
       <c r="B407" t="n">
-        <v>31285</v>
+        <v>22488</v>
       </c>
       <c r="C407" t="n">
-        <v>91.33</v>
+        <v>157.08</v>
       </c>
       <c r="D407" t="n">
-        <v>21931</v>
+        <v>29892</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>113.39</v>
+        <v>146.9</v>
       </c>
       <c r="B408" t="n">
-        <v>26225</v>
+        <v>21357</v>
       </c>
       <c r="C408" t="n">
-        <v>110.31</v>
+        <v>168.91</v>
       </c>
       <c r="D408" t="n">
-        <v>14772</v>
+        <v>10156</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>99.69</v>
+        <v>147.59</v>
       </c>
       <c r="B409" t="n">
-        <v>44266</v>
+        <v>23634</v>
       </c>
       <c r="C409" t="n">
-        <v>97</v>
+        <v>147.13</v>
       </c>
       <c r="D409" t="n">
-        <v>19971</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>109.21</v>
+        <v>147.89</v>
       </c>
       <c r="B410" t="n">
-        <v>35856</v>
+        <v>18434</v>
       </c>
       <c r="C410" t="n">
-        <v>105.53</v>
+        <v>167.94</v>
       </c>
       <c r="D410" t="n">
-        <v>17875</v>
+        <v>27547</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>94.66</v>
+        <v>148.11</v>
       </c>
       <c r="B411" t="n">
-        <v>33032</v>
+        <v>21020</v>
       </c>
       <c r="C411" t="n">
-        <v>92.87</v>
+        <v>120.31</v>
       </c>
       <c r="D411" t="n">
-        <v>11575</v>
+        <v>25692</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>103.96</v>
+        <v>148.74</v>
       </c>
       <c r="B412" t="n">
-        <v>48628</v>
+        <v>22777</v>
       </c>
       <c r="C412" t="n">
-        <v>102.02</v>
+        <v>128.88</v>
       </c>
       <c r="D412" t="n">
-        <v>11999</v>
+        <v>19122</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>105.98</v>
+        <v>149.21</v>
       </c>
       <c r="B413" t="n">
-        <v>43882</v>
+        <v>24181</v>
       </c>
       <c r="C413" t="n">
-        <v>107.66</v>
+        <v>142.64</v>
       </c>
       <c r="D413" t="n">
-        <v>20841</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>109.16</v>
+        <v>149.56</v>
       </c>
       <c r="B414" t="n">
-        <v>35030</v>
+        <v>23983</v>
       </c>
       <c r="C414" t="n">
-        <v>112.05</v>
+        <v>127.76</v>
       </c>
       <c r="D414" t="n">
-        <v>25807</v>
+        <v>24090</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>92.83</v>
+        <v>149.68</v>
       </c>
       <c r="B415" t="n">
-        <v>27822</v>
+        <v>24031</v>
       </c>
       <c r="C415" t="n">
-        <v>95.05</v>
+        <v>137.86</v>
       </c>
       <c r="D415" t="n">
-        <v>10608</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>112.45</v>
+        <v>150.33</v>
       </c>
       <c r="B416" t="n">
-        <v>24533</v>
+        <v>23344</v>
       </c>
       <c r="C416" t="n">
-        <v>113.4</v>
+        <v>132.25</v>
       </c>
       <c r="D416" t="n">
-        <v>13684</v>
+        <v>15891</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>105.7</v>
+        <v>150.38</v>
       </c>
       <c r="B417" t="n">
-        <v>46518</v>
+        <v>22259</v>
       </c>
       <c r="C417" t="n">
-        <v>105.4</v>
+        <v>180</v>
       </c>
       <c r="D417" t="n">
-        <v>27050</v>
+        <v>28680</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>114.94</v>
+        <v>150.76</v>
       </c>
       <c r="B418" t="n">
-        <v>27954</v>
+        <v>24002</v>
       </c>
       <c r="C418" t="n">
-        <v>117.68</v>
+        <v>137.23</v>
       </c>
       <c r="D418" t="n">
-        <v>19733</v>
+        <v>13744</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>100.24</v>
+        <v>151.04</v>
       </c>
       <c r="B419" t="n">
-        <v>44130</v>
+        <v>21925</v>
       </c>
       <c r="C419" t="n">
-        <v>103.28</v>
+        <v>179.27</v>
       </c>
       <c r="D419" t="n">
-        <v>27014</v>
+        <v>25405</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>99.84</v>
+        <v>151.48</v>
       </c>
       <c r="B420" t="n">
-        <v>45987</v>
+        <v>24233</v>
       </c>
       <c r="C420" t="n">
-        <v>95.93000000000001</v>
+        <v>134.44</v>
       </c>
       <c r="D420" t="n">
-        <v>13136</v>
+        <v>20905</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>112.94</v>
+        <v>151.6</v>
       </c>
       <c r="B421" t="n">
-        <v>26542</v>
+        <v>23813</v>
       </c>
       <c r="C421" t="n">
-        <v>116.75</v>
+        <v>151.23</v>
       </c>
       <c r="D421" t="n">
-        <v>29270</v>
+        <v>14436</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>92.44</v>
+        <v>152.34</v>
       </c>
       <c r="B422" t="n">
-        <v>29314</v>
+        <v>26914</v>
       </c>
       <c r="C422" t="n">
-        <v>93.42</v>
+        <v>140.38</v>
       </c>
       <c r="D422" t="n">
-        <v>11678</v>
+        <v>15315</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>112.28</v>
+        <v>152.72</v>
       </c>
       <c r="B423" t="n">
-        <v>25777</v>
+        <v>22465</v>
       </c>
       <c r="C423" t="n">
-        <v>111.41</v>
+        <v>131.62</v>
       </c>
       <c r="D423" t="n">
-        <v>23324</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>110.47</v>
+        <v>152.88</v>
       </c>
       <c r="B424" t="n">
-        <v>31366</v>
+        <v>25694</v>
       </c>
       <c r="C424" t="n">
-        <v>108.73</v>
+        <v>161.41</v>
       </c>
       <c r="D424" t="n">
-        <v>11447</v>
+        <v>23232</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>96</v>
+        <v>153.5</v>
       </c>
       <c r="B425" t="n">
-        <v>35794</v>
+        <v>26394</v>
       </c>
       <c r="C425" t="n">
-        <v>95.33</v>
+        <v>173.26</v>
       </c>
       <c r="D425" t="n">
-        <v>20100</v>
+        <v>11038</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>91</v>
+        <v>154.35</v>
       </c>
       <c r="B426" t="n">
-        <v>25202</v>
+        <v>26456</v>
       </c>
       <c r="C426" t="n">
-        <v>88.63</v>
+        <v>146.55</v>
       </c>
       <c r="D426" t="n">
-        <v>26431</v>
+        <v>14616</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>114.06</v>
+        <v>154.69</v>
       </c>
       <c r="B427" t="n">
-        <v>25028</v>
+        <v>28176</v>
       </c>
       <c r="C427" t="n">
-        <v>117.96</v>
+        <v>179.49</v>
       </c>
       <c r="D427" t="n">
-        <v>28543</v>
+        <v>16058</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>91.41</v>
+        <v>154.87</v>
       </c>
       <c r="B428" t="n">
-        <v>26683</v>
+        <v>28500</v>
       </c>
       <c r="C428" t="n">
-        <v>91.95999999999999</v>
+        <v>161.46</v>
       </c>
       <c r="D428" t="n">
-        <v>24872</v>
+        <v>16480</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>114.11</v>
+        <v>155.52</v>
       </c>
       <c r="B429" t="n">
-        <v>23731</v>
+        <v>29755</v>
       </c>
       <c r="C429" t="n">
-        <v>116.29</v>
+        <v>171.77</v>
       </c>
       <c r="D429" t="n">
-        <v>12414</v>
+        <v>13974</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>94.81999999999999</v>
+        <v>155.88</v>
       </c>
       <c r="B430" t="n">
-        <v>32067</v>
+        <v>28163</v>
       </c>
       <c r="C430" t="n">
-        <v>97.41</v>
+        <v>156.05</v>
       </c>
       <c r="D430" t="n">
-        <v>14529</v>
+        <v>29884</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>100.52</v>
+        <v>156.4</v>
       </c>
       <c r="B431" t="n">
-        <v>44360</v>
+        <v>33538</v>
       </c>
       <c r="C431" t="n">
-        <v>99.69</v>
+        <v>180</v>
       </c>
       <c r="D431" t="n">
-        <v>12277</v>
+        <v>24160</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>90.67</v>
+        <v>156.82</v>
       </c>
       <c r="B432" t="n">
-        <v>23161</v>
+        <v>28024</v>
       </c>
       <c r="C432" t="n">
-        <v>86.54000000000001</v>
+        <v>156.75</v>
       </c>
       <c r="D432" t="n">
-        <v>12576</v>
+        <v>28160</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>100.44</v>
+        <v>156.9</v>
       </c>
       <c r="B433" t="n">
-        <v>46815</v>
+        <v>29901</v>
       </c>
       <c r="C433" t="n">
-        <v>99.36</v>
+        <v>135.4</v>
       </c>
       <c r="D433" t="n">
-        <v>25486</v>
+        <v>11344</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>91.59999999999999</v>
+        <v>157.82</v>
       </c>
       <c r="B434" t="n">
-        <v>26634</v>
+        <v>30146</v>
       </c>
       <c r="C434" t="n">
-        <v>91.98999999999999</v>
+        <v>128.87</v>
       </c>
       <c r="D434" t="n">
-        <v>29527</v>
+        <v>20763</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>116.15</v>
+        <v>157.98</v>
       </c>
       <c r="B435" t="n">
-        <v>24638</v>
+        <v>29257</v>
       </c>
       <c r="C435" t="n">
-        <v>115.53</v>
+        <v>136.65</v>
       </c>
       <c r="D435" t="n">
-        <v>19610</v>
+        <v>20072</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>98.06999999999999</v>
+        <v>159.16</v>
       </c>
       <c r="B436" t="n">
-        <v>38951</v>
+        <v>32577</v>
       </c>
       <c r="C436" t="n">
-        <v>100.2</v>
+        <v>163.64</v>
       </c>
       <c r="D436" t="n">
-        <v>15370</v>
+        <v>19556</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>103.24</v>
+        <v>159.41</v>
       </c>
       <c r="B437" t="n">
-        <v>45685</v>
+        <v>28384</v>
       </c>
       <c r="C437" t="n">
-        <v>99.23999999999999</v>
+        <v>164.93</v>
       </c>
       <c r="D437" t="n">
-        <v>10177</v>
+        <v>10904</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>84.78</v>
+        <v>159.81</v>
       </c>
       <c r="B438" t="n">
-        <v>25745</v>
+        <v>31214</v>
       </c>
       <c r="C438" t="n">
-        <v>82.88</v>
+        <v>157.17</v>
       </c>
       <c r="D438" t="n">
-        <v>28736</v>
+        <v>28976</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>129.9</v>
+        <v>160.19</v>
       </c>
       <c r="B439" t="n">
-        <v>25357</v>
+        <v>30073</v>
       </c>
       <c r="C439" t="n">
-        <v>129.45</v>
+        <v>177.34</v>
       </c>
       <c r="D439" t="n">
-        <v>28161</v>
+        <v>11846</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>144.94</v>
+        <v>160.59</v>
       </c>
       <c r="B440" t="n">
-        <v>23878</v>
+        <v>29681</v>
       </c>
       <c r="C440" t="n">
-        <v>139.51</v>
+        <v>179.84</v>
       </c>
       <c r="D440" t="n">
-        <v>21242</v>
+        <v>22178</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>95.61</v>
+        <v>160.98</v>
       </c>
       <c r="B441" t="n">
-        <v>35424</v>
+        <v>30931</v>
       </c>
       <c r="C441" t="n">
-        <v>91.34</v>
+        <v>131.17</v>
       </c>
       <c r="D441" t="n">
-        <v>18113</v>
+        <v>10090</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>94.67</v>
+        <v>161.07</v>
       </c>
       <c r="B442" t="n">
-        <v>33048</v>
+        <v>31281</v>
       </c>
       <c r="C442" t="n">
-        <v>93.97</v>
+        <v>165.32</v>
       </c>
       <c r="D442" t="n">
-        <v>14351</v>
+        <v>23408</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>114.29</v>
+        <v>161.5</v>
       </c>
       <c r="B443" t="n">
-        <v>23771</v>
+        <v>29431</v>
       </c>
       <c r="C443" t="n">
-        <v>117.64</v>
+        <v>160.92</v>
       </c>
       <c r="D443" t="n">
-        <v>19991</v>
+        <v>17947</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>105.29</v>
+        <v>162.03</v>
       </c>
       <c r="B444" t="n">
-        <v>42002</v>
+        <v>32679</v>
       </c>
       <c r="C444" t="n">
-        <v>105.82</v>
+        <v>133.33</v>
       </c>
       <c r="D444" t="n">
-        <v>15257</v>
+        <v>17557</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>90.34999999999999</v>
+        <v>162.18</v>
       </c>
       <c r="B445" t="n">
-        <v>21593</v>
+        <v>32895</v>
       </c>
       <c r="C445" t="n">
-        <v>88.54000000000001</v>
+        <v>178.03</v>
       </c>
       <c r="D445" t="n">
-        <v>27171</v>
+        <v>28793</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>92.87</v>
+        <v>162.32</v>
       </c>
       <c r="B446" t="n">
-        <v>27805</v>
+        <v>27892</v>
       </c>
       <c r="C446" t="n">
-        <v>93.39</v>
+        <v>134.29</v>
       </c>
       <c r="D446" t="n">
-        <v>16785</v>
+        <v>17092</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>95.73</v>
+        <v>162.42</v>
       </c>
       <c r="B447" t="n">
-        <v>33632</v>
+        <v>28985</v>
       </c>
       <c r="C447" t="n">
-        <v>96.38</v>
+        <v>147.23</v>
       </c>
       <c r="D447" t="n">
-        <v>26598</v>
+        <v>15328</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>106.93</v>
+        <v>163.21</v>
       </c>
       <c r="B448" t="n">
-        <v>45805</v>
+        <v>31489</v>
       </c>
       <c r="C448" t="n">
-        <v>108.39</v>
+        <v>175.63</v>
       </c>
       <c r="D448" t="n">
-        <v>29110</v>
+        <v>17365</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>104.09</v>
+        <v>163.36</v>
       </c>
       <c r="B449" t="n">
-        <v>44442</v>
+        <v>29585</v>
       </c>
       <c r="C449" t="n">
-        <v>103.88</v>
+        <v>168.17</v>
       </c>
       <c r="D449" t="n">
-        <v>23780</v>
+        <v>17235</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>94.06999999999999</v>
+        <v>164.06</v>
       </c>
       <c r="B450" t="n">
-        <v>27774</v>
+        <v>25671</v>
       </c>
       <c r="C450" t="n">
-        <v>95.61</v>
+        <v>180</v>
       </c>
       <c r="D450" t="n">
-        <v>25480</v>
+        <v>22314</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>95.29000000000001</v>
+        <v>164.11</v>
       </c>
       <c r="B451" t="n">
-        <v>35294</v>
+        <v>29541</v>
       </c>
       <c r="C451" t="n">
-        <v>92.05</v>
+        <v>180</v>
       </c>
       <c r="D451" t="n">
-        <v>28151</v>
+        <v>11691</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>90.84999999999999</v>
+        <v>164.8</v>
       </c>
       <c r="B452" t="n">
-        <v>23449</v>
+        <v>29283</v>
       </c>
       <c r="C452" t="n">
-        <v>93.94</v>
+        <v>133.22</v>
       </c>
       <c r="D452" t="n">
-        <v>13155</v>
+        <v>20429</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>28.28</v>
+        <v>164.94</v>
       </c>
       <c r="B453" t="n">
-        <v>21306</v>
+        <v>29780</v>
       </c>
       <c r="C453" t="n">
-        <v>28.69</v>
+        <v>147.68</v>
       </c>
       <c r="D453" t="n">
-        <v>10537</v>
+        <v>14464</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>108.82</v>
+        <v>165.06</v>
       </c>
       <c r="B454" t="n">
-        <v>37771</v>
+        <v>28814</v>
       </c>
       <c r="C454" t="n">
-        <v>106.43</v>
+        <v>165.07</v>
       </c>
       <c r="D454" t="n">
-        <v>29588</v>
+        <v>23090</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>93.5</v>
+        <v>165.25</v>
       </c>
       <c r="B455" t="n">
-        <v>28583</v>
+        <v>27549</v>
       </c>
       <c r="C455" t="n">
-        <v>96.15000000000001</v>
+        <v>160.15</v>
       </c>
       <c r="D455" t="n">
-        <v>12617</v>
+        <v>14860</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>100.17</v>
+        <v>165.47</v>
       </c>
       <c r="B456" t="n">
-        <v>42835</v>
+        <v>28267</v>
       </c>
       <c r="C456" t="n">
-        <v>98.48999999999999</v>
+        <v>176.39</v>
       </c>
       <c r="D456" t="n">
-        <v>15708</v>
+        <v>25978</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>99.13</v>
+        <v>165.57</v>
       </c>
       <c r="B457" t="n">
-        <v>41579</v>
+        <v>27656</v>
       </c>
       <c r="C457" t="n">
-        <v>93.92</v>
+        <v>178.7</v>
       </c>
       <c r="D457" t="n">
-        <v>19937</v>
+        <v>15582</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>101.04</v>
+        <v>165.85</v>
       </c>
       <c r="B458" t="n">
-        <v>45371</v>
+        <v>29590</v>
       </c>
       <c r="C458" t="n">
-        <v>97.54000000000001</v>
+        <v>166.37</v>
       </c>
       <c r="D458" t="n">
-        <v>13556</v>
+        <v>28413</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>101.75</v>
+        <v>165.96</v>
       </c>
       <c r="B459" t="n">
-        <v>47193</v>
+        <v>28797</v>
       </c>
       <c r="C459" t="n">
-        <v>104.6</v>
+        <v>180</v>
       </c>
       <c r="D459" t="n">
-        <v>24697</v>
+        <v>18489</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>62.89</v>
+        <v>166.09</v>
       </c>
       <c r="B460" t="n">
-        <v>23851</v>
+        <v>26257</v>
       </c>
       <c r="C460" t="n">
-        <v>64.87</v>
+        <v>174.8</v>
       </c>
       <c r="D460" t="n">
-        <v>25790</v>
+        <v>21495</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>92.52</v>
+        <v>166.18</v>
       </c>
       <c r="B461" t="n">
-        <v>25333</v>
+        <v>27796</v>
       </c>
       <c r="C461" t="n">
-        <v>93.3</v>
+        <v>156.86</v>
       </c>
       <c r="D461" t="n">
-        <v>20565</v>
+        <v>27527</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>98.25</v>
+        <v>166.58</v>
       </c>
       <c r="B462" t="n">
-        <v>40322</v>
+        <v>26791</v>
       </c>
       <c r="C462" t="n">
-        <v>99.31999999999999</v>
+        <v>162.18</v>
       </c>
       <c r="D462" t="n">
-        <v>19888</v>
+        <v>26270</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>99.11</v>
+        <v>166.99</v>
       </c>
       <c r="B463" t="n">
-        <v>42493</v>
+        <v>26425</v>
       </c>
       <c r="C463" t="n">
-        <v>98.23999999999999</v>
+        <v>170.23</v>
       </c>
       <c r="D463" t="n">
-        <v>27574</v>
+        <v>24174</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>112.27</v>
+        <v>167.69</v>
       </c>
       <c r="B464" t="n">
-        <v>28724</v>
+        <v>25444</v>
       </c>
       <c r="C464" t="n">
-        <v>111.57</v>
+        <v>167.62</v>
       </c>
       <c r="D464" t="n">
-        <v>11383</v>
+        <v>23160</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>130.25</v>
+        <v>167.78</v>
       </c>
       <c r="B465" t="n">
-        <v>22653</v>
+        <v>23679</v>
       </c>
       <c r="C465" t="n">
-        <v>129.27</v>
+        <v>167.77</v>
       </c>
       <c r="D465" t="n">
-        <v>16769</v>
+        <v>28144</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>105.25</v>
+        <v>168.67</v>
       </c>
       <c r="B466" t="n">
-        <v>45315</v>
+        <v>25099</v>
       </c>
       <c r="C466" t="n">
-        <v>106.82</v>
+        <v>152.76</v>
       </c>
       <c r="D466" t="n">
-        <v>27935</v>
+        <v>22560</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>101.85</v>
+        <v>168.68</v>
       </c>
       <c r="B467" t="n">
-        <v>47510</v>
+        <v>24428</v>
       </c>
       <c r="C467" t="n">
-        <v>101.91</v>
+        <v>180</v>
       </c>
       <c r="D467" t="n">
-        <v>22493</v>
+        <v>16466</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>103.26</v>
+        <v>168.81</v>
       </c>
       <c r="B468" t="n">
-        <v>46439</v>
+        <v>24058</v>
       </c>
       <c r="C468" t="n">
-        <v>101.97</v>
+        <v>146.82</v>
       </c>
       <c r="D468" t="n">
-        <v>10379</v>
+        <v>25590</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>105.67</v>
+        <v>169.16</v>
       </c>
       <c r="B469" t="n">
-        <v>43768</v>
+        <v>25071</v>
       </c>
       <c r="C469" t="n">
-        <v>108.94</v>
+        <v>169.98</v>
       </c>
       <c r="D469" t="n">
-        <v>22161</v>
+        <v>27539</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>99.34999999999999</v>
+        <v>170.08</v>
       </c>
       <c r="B470" t="n">
-        <v>41261</v>
+        <v>24012</v>
       </c>
       <c r="C470" t="n">
-        <v>99.90000000000001</v>
+        <v>180</v>
       </c>
       <c r="D470" t="n">
-        <v>11630</v>
+        <v>27733</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>97.39</v>
+        <v>170.08</v>
       </c>
       <c r="B471" t="n">
-        <v>40151</v>
+        <v>22863</v>
       </c>
       <c r="C471" t="n">
-        <v>98.8</v>
+        <v>162.69</v>
       </c>
       <c r="D471" t="n">
-        <v>11374</v>
+        <v>26284</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>111.23</v>
+        <v>170.14</v>
       </c>
       <c r="B472" t="n">
-        <v>28811</v>
+        <v>22202</v>
       </c>
       <c r="C472" t="n">
-        <v>106.34</v>
+        <v>143.33</v>
       </c>
       <c r="D472" t="n">
-        <v>13046</v>
+        <v>29349</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>104.89</v>
+        <v>170.41</v>
       </c>
       <c r="B473" t="n">
-        <v>45407</v>
+        <v>23100</v>
       </c>
       <c r="C473" t="n">
-        <v>104.42</v>
+        <v>170.24</v>
       </c>
       <c r="D473" t="n">
-        <v>10945</v>
+        <v>17905</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>106.04</v>
+        <v>170.81</v>
       </c>
       <c r="B474" t="n">
-        <v>46123</v>
+        <v>20734</v>
       </c>
       <c r="C474" t="n">
-        <v>103.23</v>
+        <v>157.08</v>
       </c>
       <c r="D474" t="n">
-        <v>25035</v>
+        <v>27202</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>101.5</v>
+        <v>170.98</v>
       </c>
       <c r="B475" t="n">
-        <v>46243</v>
+        <v>22996</v>
       </c>
       <c r="C475" t="n">
-        <v>100.02</v>
+        <v>179.21</v>
       </c>
       <c r="D475" t="n">
-        <v>24071</v>
+        <v>11188</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>90.79000000000001</v>
+        <v>171.28</v>
       </c>
       <c r="B476" t="n">
-        <v>26207</v>
+        <v>21809</v>
       </c>
       <c r="C476" t="n">
-        <v>90.23999999999999</v>
+        <v>180</v>
       </c>
       <c r="D476" t="n">
-        <v>19407</v>
+        <v>27159</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>105.83</v>
+        <v>171.37</v>
       </c>
       <c r="B477" t="n">
-        <v>46783</v>
+        <v>21002</v>
       </c>
       <c r="C477" t="n">
-        <v>103.91</v>
+        <v>156</v>
       </c>
       <c r="D477" t="n">
-        <v>11096</v>
+        <v>19930</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>97.34999999999999</v>
+        <v>171.68</v>
       </c>
       <c r="B478" t="n">
-        <v>39404</v>
+        <v>22908</v>
       </c>
       <c r="C478" t="n">
-        <v>100.8</v>
+        <v>141.69</v>
       </c>
       <c r="D478" t="n">
-        <v>27989</v>
+        <v>28468</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>99.40000000000001</v>
+        <v>172.01</v>
       </c>
       <c r="B479" t="n">
-        <v>45381</v>
+        <v>21673</v>
       </c>
       <c r="C479" t="n">
-        <v>103.29</v>
+        <v>164.08</v>
       </c>
       <c r="D479" t="n">
-        <v>18549</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>91.09</v>
+        <v>172.21</v>
       </c>
       <c r="B480" t="n">
-        <v>22932</v>
+        <v>21824</v>
       </c>
       <c r="C480" t="n">
-        <v>88.25</v>
+        <v>180</v>
       </c>
       <c r="D480" t="n">
-        <v>16640</v>
+        <v>27816</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>98.11</v>
+        <v>172.81</v>
       </c>
       <c r="B481" t="n">
-        <v>40029</v>
+        <v>20695</v>
       </c>
       <c r="C481" t="n">
-        <v>98.43000000000001</v>
+        <v>178.02</v>
       </c>
       <c r="D481" t="n">
-        <v>28121</v>
+        <v>25775</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>100.91</v>
+        <v>173.01</v>
       </c>
       <c r="B482" t="n">
-        <v>44804</v>
+        <v>18318</v>
       </c>
       <c r="C482" t="n">
-        <v>101.37</v>
+        <v>179.64</v>
       </c>
       <c r="D482" t="n">
-        <v>25477</v>
+        <v>22448</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>114.3</v>
+        <v>173.32</v>
       </c>
       <c r="B483" t="n">
-        <v>23898</v>
+        <v>20960</v>
       </c>
       <c r="C483" t="n">
-        <v>113.39</v>
+        <v>180</v>
       </c>
       <c r="D483" t="n">
-        <v>16188</v>
+        <v>15565</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>112.93</v>
+        <v>173.69</v>
       </c>
       <c r="B484" t="n">
-        <v>23103</v>
+        <v>18898</v>
       </c>
       <c r="C484" t="n">
-        <v>108.9</v>
+        <v>174.22</v>
       </c>
       <c r="D484" t="n">
-        <v>19591</v>
+        <v>16657</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>93.73999999999999</v>
+        <v>174.1</v>
       </c>
       <c r="B485" t="n">
-        <v>30885</v>
+        <v>20728</v>
       </c>
       <c r="C485" t="n">
-        <v>91.92</v>
+        <v>180</v>
       </c>
       <c r="D485" t="n">
-        <v>13781</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>113.38</v>
+        <v>174.38</v>
       </c>
       <c r="B486" t="n">
-        <v>23993</v>
+        <v>21491</v>
       </c>
       <c r="C486" t="n">
-        <v>111.85</v>
+        <v>156.16</v>
       </c>
       <c r="D486" t="n">
-        <v>29946</v>
+        <v>22233</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>145.12</v>
+        <v>174.6</v>
       </c>
       <c r="B487" t="n">
-        <v>21514</v>
+        <v>19681</v>
       </c>
       <c r="C487" t="n">
-        <v>146.29</v>
+        <v>146.62</v>
       </c>
       <c r="D487" t="n">
-        <v>26911</v>
+        <v>15708</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>108.99</v>
+        <v>174.72</v>
       </c>
       <c r="B488" t="n">
-        <v>34173</v>
+        <v>18876</v>
       </c>
       <c r="C488" t="n">
-        <v>107.74</v>
+        <v>159.45</v>
       </c>
       <c r="D488" t="n">
-        <v>17552</v>
+        <v>21216</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>111.58</v>
+        <v>175.02</v>
       </c>
       <c r="B489" t="n">
-        <v>29806</v>
+        <v>17662</v>
       </c>
       <c r="C489" t="n">
-        <v>107.77</v>
+        <v>176.34</v>
       </c>
       <c r="D489" t="n">
-        <v>23194</v>
+        <v>21298</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>103.01</v>
+        <v>175.28</v>
       </c>
       <c r="B490" t="n">
-        <v>45465</v>
+        <v>19289</v>
       </c>
       <c r="C490" t="n">
-        <v>103.2</v>
+        <v>172.93</v>
       </c>
       <c r="D490" t="n">
-        <v>24347</v>
+        <v>20917</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>95.23</v>
+        <v>175.56</v>
       </c>
       <c r="B491" t="n">
-        <v>33189</v>
+        <v>20236</v>
       </c>
       <c r="C491" t="n">
-        <v>96.23</v>
+        <v>155.5</v>
       </c>
       <c r="D491" t="n">
-        <v>16077</v>
+        <v>12369</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>50.95</v>
+        <v>176.37</v>
       </c>
       <c r="B492" t="n">
-        <v>22416</v>
+        <v>19104</v>
       </c>
       <c r="C492" t="n">
-        <v>53.28</v>
+        <v>179.14</v>
       </c>
       <c r="D492" t="n">
-        <v>11122</v>
+        <v>26993</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>111.53</v>
+        <v>176.46</v>
       </c>
       <c r="B493" t="n">
-        <v>27127</v>
+        <v>20632</v>
       </c>
       <c r="C493" t="n">
-        <v>110.68</v>
+        <v>180</v>
       </c>
       <c r="D493" t="n">
-        <v>10664</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>111.09</v>
+        <v>176.88</v>
       </c>
       <c r="B494" t="n">
-        <v>26274</v>
+        <v>17910</v>
       </c>
       <c r="C494" t="n">
-        <v>113.17</v>
+        <v>180</v>
       </c>
       <c r="D494" t="n">
-        <v>16768</v>
+        <v>25042</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>94.06</v>
+        <v>176.93</v>
       </c>
       <c r="B495" t="n">
-        <v>33665</v>
+        <v>20171</v>
       </c>
       <c r="C495" t="n">
-        <v>90.53</v>
+        <v>180</v>
       </c>
       <c r="D495" t="n">
-        <v>20263</v>
+        <v>25952</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>114.24</v>
+        <v>177</v>
       </c>
       <c r="B496" t="n">
-        <v>23358</v>
+        <v>17702</v>
       </c>
       <c r="C496" t="n">
-        <v>111.53</v>
+        <v>156.83</v>
       </c>
       <c r="D496" t="n">
-        <v>17657</v>
+        <v>22333</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>103.53</v>
+        <v>177.38</v>
       </c>
       <c r="B497" t="n">
-        <v>47886</v>
+        <v>18092</v>
       </c>
       <c r="C497" t="n">
-        <v>100.14</v>
+        <v>166.58</v>
       </c>
       <c r="D497" t="n">
-        <v>19644</v>
+        <v>18119</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>29.56</v>
+        <v>177.67</v>
       </c>
       <c r="B498" t="n">
-        <v>22470</v>
+        <v>20413</v>
       </c>
       <c r="C498" t="n">
-        <v>28.18</v>
+        <v>178.65</v>
       </c>
       <c r="D498" t="n">
-        <v>26747</v>
+        <v>18170</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>91.27</v>
+        <v>177.74</v>
       </c>
       <c r="B499" t="n">
-        <v>24745</v>
+        <v>19083</v>
       </c>
       <c r="C499" t="n">
-        <v>90.8</v>
+        <v>168.4</v>
       </c>
       <c r="D499" t="n">
-        <v>17021</v>
+        <v>18465</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>171.31</v>
+        <v>178.92</v>
       </c>
       <c r="B500" t="n">
-        <v>26473</v>
+        <v>16810</v>
       </c>
       <c r="C500" t="n">
-        <v>170.73</v>
+        <v>144.64</v>
       </c>
       <c r="D500" t="n">
-        <v>10567</v>
+        <v>17761</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>90.25</v>
+        <v>179.45</v>
       </c>
       <c r="B501" t="n">
-        <v>25570</v>
+        <v>18936</v>
       </c>
       <c r="C501" t="n">
-        <v>87.41</v>
+        <v>180</v>
       </c>
       <c r="D501" t="n">
-        <v>17496</v>
+        <v>19510</v>
       </c>
     </row>
   </sheetData>
